--- a/Chanthadara_territory_chart.xlsx
+++ b/Chanthadara_territory_chart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chimm\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC6C3575-DDED-4C88-9C10-9C2866078547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8581C3D3-C9FE-4795-B4F7-EB785FA774EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4F9622DB-3F0B-4399-96EC-3CBDB6BB25F8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{4F9622DB-3F0B-4399-96EC-3CBDB6BB25F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Findings" sheetId="7" r:id="rId1"/>
@@ -26,10 +26,10 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId5"/>
-    <pivotCache cacheId="14" r:id="rId6"/>
-    <pivotCache cacheId="21" r:id="rId7"/>
-    <pivotCache cacheId="26" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId6"/>
+    <pivotCache cacheId="2" r:id="rId7"/>
+    <pivotCache cacheId="3" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -235,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -244,10 +244,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -379,43 +377,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="12700">
-              <a:solidFill>
-                <a:schemeClr val="lt2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1070,17 +1032,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="8"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1355,6 +1307,26 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-48F8-4410-BCF9-56C98C67EEB2}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-48F8-4410-BCF9-56C98C67EEB2}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
@@ -1871,19 +1843,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -2294,7 +2254,7 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
+      <c:overlay val="1"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -2337,20 +2297,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="4"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -2424,20 +2371,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="4"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
+            <c:symbol val="none"/>
           </c:marker>
           <c:cat>
             <c:multiLvlStrRef>
@@ -2790,7 +2724,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:dropLines>
-        <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="612486479"/>
         <c:axId val="612486959"/>
@@ -2942,7 +2875,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Total Revenue</a:t>
+                  <a:t>Total revenue</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -7953,7 +7886,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6B0FE92-A8F0-44F2-81AE-8F660C0D359C}" name="PivotTable7" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6B0FE92-A8F0-44F2-81AE-8F660C0D359C}" name="PivotTable7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="A47:B54" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField showAll="0">
@@ -8045,7 +7978,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CD5EED47-6634-433F-8246-8166C77A8301}" name="PivotTable6" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6" rowHeaderCaption="Territory">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CD5EED47-6634-433F-8246-8166C77A8301}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6" rowHeaderCaption="Territory">
   <location ref="A7:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" showAll="0">
@@ -8125,7 +8058,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4F5F414B-C686-4F7F-BA97-F099CE7B7DB1}" name="PivotTable4" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18" rowHeaderCaption="Store Location">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4F5F414B-C686-4F7F-BA97-F099CE7B7DB1}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18" rowHeaderCaption="Store Location">
   <location ref="A25:B37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField showAll="0">
@@ -8257,7 +8190,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6BFC6F99-E6B7-4784-8CBE-342B2F900FC9}" name="PivotTable2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6BFC6F99-E6B7-4784-8CBE-342B2F900FC9}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
   <location ref="A1:B54" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -8906,7 +8839,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>25</v>
       </c>
     </row>
@@ -8919,7 +8852,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" t="s">
         <v>23</v>
       </c>
       <c r="B3">
@@ -8927,7 +8860,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="B4">
@@ -8935,10 +8868,9 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="7"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -8955,7 +8887,7 @@
       <c r="A9">
         <v>905</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" t="s">
         <v>8</v>
       </c>
       <c r="C9">
@@ -8966,7 +8898,7 @@
       <c r="A10">
         <v>910</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" t="s">
         <v>9</v>
       </c>
       <c r="C10">
@@ -8977,7 +8909,7 @@
       <c r="A11">
         <v>909</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" t="s">
         <v>10</v>
       </c>
       <c r="C11">
@@ -8988,7 +8920,7 @@
       <c r="A12">
         <v>906</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" t="s">
         <v>11</v>
       </c>
       <c r="C12">
@@ -8999,7 +8931,7 @@
       <c r="A13">
         <v>904</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13">
@@ -9010,7 +8942,7 @@
       <c r="A14">
         <v>908</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" t="s">
         <v>13</v>
       </c>
       <c r="C14">
@@ -9021,7 +8953,7 @@
       <c r="A15">
         <v>901</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" t="s">
         <v>14</v>
       </c>
       <c r="C15">
@@ -9032,7 +8964,7 @@
       <c r="A16">
         <v>902</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" t="s">
         <v>15</v>
       </c>
       <c r="C16">
@@ -9043,7 +8975,7 @@
       <c r="A17">
         <v>903</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" t="s">
         <v>16</v>
       </c>
       <c r="C17">
@@ -9054,7 +8986,7 @@
       <c r="A18">
         <v>911</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" t="s">
         <v>17</v>
       </c>
       <c r="C18">
@@ -9065,7 +8997,7 @@
       <c r="A19">
         <v>907</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" t="s">
         <v>18</v>
       </c>
       <c r="C19">
@@ -9073,7 +9005,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
     </row>
@@ -9101,7 +9033,7 @@
       <c r="B24">
         <v>1</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" t="s">
         <v>31</v>
       </c>
       <c r="D24">
@@ -9118,7 +9050,7 @@
       <c r="B25">
         <v>1</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" t="s">
         <v>32</v>
       </c>
       <c r="D25">
@@ -9135,7 +9067,7 @@
       <c r="B26">
         <v>1</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" t="s">
         <v>33</v>
       </c>
       <c r="D26">
@@ -9152,7 +9084,7 @@
       <c r="B27">
         <v>1</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" t="s">
         <v>34</v>
       </c>
       <c r="D27">
@@ -9169,7 +9101,7 @@
       <c r="B28">
         <v>1</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" t="s">
         <v>35</v>
       </c>
       <c r="D28">
@@ -9186,7 +9118,7 @@
       <c r="B29">
         <v>1</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" t="s">
         <v>36</v>
       </c>
       <c r="D29">
@@ -9203,7 +9135,7 @@
       <c r="B30">
         <v>2</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" t="s">
         <v>31</v>
       </c>
       <c r="D30">
@@ -9220,7 +9152,7 @@
       <c r="B31">
         <v>2</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" t="s">
         <v>32</v>
       </c>
       <c r="D31">
@@ -9237,7 +9169,7 @@
       <c r="B32">
         <v>2</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" t="s">
         <v>33</v>
       </c>
       <c r="D32">
@@ -9254,7 +9186,7 @@
       <c r="B33">
         <v>2</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" t="s">
         <v>34</v>
       </c>
       <c r="D33">
@@ -9271,7 +9203,7 @@
       <c r="B34">
         <v>2</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" t="s">
         <v>35</v>
       </c>
       <c r="D34">
@@ -9288,7 +9220,7 @@
       <c r="B35">
         <v>2</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" t="s">
         <v>36</v>
       </c>
       <c r="D35">
@@ -9305,7 +9237,7 @@
       <c r="B36">
         <v>3</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" t="s">
         <v>31</v>
       </c>
       <c r="D36">
@@ -9322,7 +9254,7 @@
       <c r="B37">
         <v>3</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" t="s">
         <v>32</v>
       </c>
       <c r="D37">
@@ -9339,7 +9271,7 @@
       <c r="B38">
         <v>3</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" t="s">
         <v>33</v>
       </c>
       <c r="D38">
@@ -9356,7 +9288,7 @@
       <c r="B39">
         <v>3</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" t="s">
         <v>34</v>
       </c>
       <c r="D39">
@@ -9373,7 +9305,7 @@
       <c r="B40">
         <v>3</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" t="s">
         <v>35</v>
       </c>
       <c r="D40">
@@ -9390,7 +9322,7 @@
       <c r="B41">
         <v>3</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" t="s">
         <v>36</v>
       </c>
       <c r="D41">
@@ -9407,7 +9339,7 @@
       <c r="B42">
         <v>4</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" t="s">
         <v>31</v>
       </c>
       <c r="D42">
@@ -9424,7 +9356,7 @@
       <c r="B43">
         <v>4</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" t="s">
         <v>32</v>
       </c>
       <c r="D43">
@@ -9441,7 +9373,7 @@
       <c r="B44">
         <v>4</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" t="s">
         <v>33</v>
       </c>
       <c r="D44">
@@ -9458,7 +9390,7 @@
       <c r="B45">
         <v>4</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" t="s">
         <v>34</v>
       </c>
       <c r="D45">
@@ -9475,7 +9407,7 @@
       <c r="B46">
         <v>4</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" t="s">
         <v>35</v>
       </c>
       <c r="D46">
@@ -9492,7 +9424,7 @@
       <c r="B47">
         <v>4</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" t="s">
         <v>36</v>
       </c>
       <c r="D47">
@@ -9509,7 +9441,7 @@
       <c r="B48">
         <v>5</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" t="s">
         <v>31</v>
       </c>
       <c r="D48">
@@ -9526,7 +9458,7 @@
       <c r="B49">
         <v>5</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" t="s">
         <v>32</v>
       </c>
       <c r="D49">
@@ -9543,7 +9475,7 @@
       <c r="B50">
         <v>5</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" t="s">
         <v>33</v>
       </c>
       <c r="D50">
@@ -9560,7 +9492,7 @@
       <c r="B51">
         <v>5</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" t="s">
         <v>34</v>
       </c>
       <c r="D51">
@@ -9577,7 +9509,7 @@
       <c r="B52">
         <v>5</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" t="s">
         <v>35</v>
       </c>
       <c r="D52">
@@ -9594,7 +9526,7 @@
       <c r="B53">
         <v>5</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" t="s">
         <v>36</v>
       </c>
       <c r="D53">
@@ -9611,7 +9543,7 @@
       <c r="B54">
         <v>6</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" t="s">
         <v>31</v>
       </c>
       <c r="D54">
@@ -9628,7 +9560,7 @@
       <c r="B55">
         <v>6</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" t="s">
         <v>32</v>
       </c>
       <c r="D55">
@@ -9645,7 +9577,7 @@
       <c r="B56">
         <v>6</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" t="s">
         <v>33</v>
       </c>
       <c r="D56">
@@ -9662,7 +9594,7 @@
       <c r="B57">
         <v>6</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" t="s">
         <v>34</v>
       </c>
       <c r="D57">
@@ -9679,7 +9611,7 @@
       <c r="B58">
         <v>6</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" t="s">
         <v>35</v>
       </c>
       <c r="D58">
@@ -9696,7 +9628,7 @@
       <c r="B59">
         <v>6</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" t="s">
         <v>36</v>
       </c>
       <c r="D59">
@@ -9713,7 +9645,7 @@
       <c r="B60">
         <v>7</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" t="s">
         <v>31</v>
       </c>
       <c r="D60">
@@ -9730,7 +9662,7 @@
       <c r="B61">
         <v>7</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" t="s">
         <v>32</v>
       </c>
       <c r="D61">
@@ -9747,7 +9679,7 @@
       <c r="B62">
         <v>7</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" t="s">
         <v>33</v>
       </c>
       <c r="D62">
@@ -9764,7 +9696,7 @@
       <c r="B63">
         <v>7</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" t="s">
         <v>34</v>
       </c>
       <c r="D63">
@@ -9781,7 +9713,7 @@
       <c r="B64">
         <v>7</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" t="s">
         <v>35</v>
       </c>
       <c r="D64">
@@ -9798,7 +9730,7 @@
       <c r="B65">
         <v>7</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" t="s">
         <v>36</v>
       </c>
       <c r="D65">
@@ -9815,7 +9747,7 @@
       <c r="B66">
         <v>8</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" t="s">
         <v>31</v>
       </c>
       <c r="D66">
@@ -9832,7 +9764,7 @@
       <c r="B67">
         <v>8</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C67" t="s">
         <v>32</v>
       </c>
       <c r="D67">
@@ -9849,7 +9781,7 @@
       <c r="B68">
         <v>8</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" t="s">
         <v>33</v>
       </c>
       <c r="D68">
@@ -9866,7 +9798,7 @@
       <c r="B69">
         <v>8</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" t="s">
         <v>34</v>
       </c>
       <c r="D69">
@@ -9883,7 +9815,7 @@
       <c r="B70">
         <v>8</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" t="s">
         <v>35</v>
       </c>
       <c r="D70">
@@ -9900,7 +9832,7 @@
       <c r="B71">
         <v>8</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C71" t="s">
         <v>36</v>
       </c>
       <c r="D71">
@@ -9917,7 +9849,7 @@
       <c r="B72">
         <v>9</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" t="s">
         <v>31</v>
       </c>
       <c r="D72">
@@ -9934,7 +9866,7 @@
       <c r="B73">
         <v>9</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="C73" t="s">
         <v>32</v>
       </c>
       <c r="D73">
@@ -9951,7 +9883,7 @@
       <c r="B74">
         <v>9</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" t="s">
         <v>33</v>
       </c>
       <c r="D74">
@@ -9968,7 +9900,7 @@
       <c r="B75">
         <v>9</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" t="s">
         <v>34</v>
       </c>
       <c r="D75">
@@ -9985,7 +9917,7 @@
       <c r="B76">
         <v>9</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" t="s">
         <v>35</v>
       </c>
       <c r="D76">
@@ -10002,7 +9934,7 @@
       <c r="B77">
         <v>9</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C77" t="s">
         <v>36</v>
       </c>
       <c r="D77">
@@ -10019,7 +9951,7 @@
       <c r="B78">
         <v>10</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="C78" t="s">
         <v>31</v>
       </c>
       <c r="D78">
@@ -10036,7 +9968,7 @@
       <c r="B79">
         <v>10</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C79" t="s">
         <v>32</v>
       </c>
       <c r="D79">
@@ -10053,7 +9985,7 @@
       <c r="B80">
         <v>10</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="C80" t="s">
         <v>33</v>
       </c>
       <c r="D80">
@@ -10070,7 +10002,7 @@
       <c r="B81">
         <v>10</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" t="s">
         <v>34</v>
       </c>
       <c r="D81">
@@ -10087,7 +10019,7 @@
       <c r="B82">
         <v>10</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="C82" t="s">
         <v>35</v>
       </c>
       <c r="D82">
@@ -10104,7 +10036,7 @@
       <c r="B83">
         <v>10</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="C83" t="s">
         <v>36</v>
       </c>
       <c r="D83">
@@ -10121,7 +10053,7 @@
       <c r="B84">
         <v>11</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="C84" t="s">
         <v>31</v>
       </c>
       <c r="D84">
@@ -10138,7 +10070,7 @@
       <c r="B85">
         <v>11</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C85" t="s">
         <v>32</v>
       </c>
       <c r="D85">
@@ -10155,7 +10087,7 @@
       <c r="B86">
         <v>11</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="C86" t="s">
         <v>33</v>
       </c>
       <c r="D86">
@@ -10172,7 +10104,7 @@
       <c r="B87">
         <v>11</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="C87" t="s">
         <v>34</v>
       </c>
       <c r="D87">
@@ -10189,7 +10121,7 @@
       <c r="B88">
         <v>11</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="C88" t="s">
         <v>35</v>
       </c>
       <c r="D88">
@@ -10206,7 +10138,7 @@
       <c r="B89">
         <v>11</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="C89" t="s">
         <v>36</v>
       </c>
       <c r="D89">
@@ -10223,7 +10155,7 @@
       <c r="B90">
         <v>12</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="C90" t="s">
         <v>31</v>
       </c>
       <c r="D90">
@@ -10240,7 +10172,7 @@
       <c r="B91">
         <v>12</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="C91" t="s">
         <v>32</v>
       </c>
       <c r="D91">
@@ -10257,7 +10189,7 @@
       <c r="B92">
         <v>12</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="C92" t="s">
         <v>33</v>
       </c>
       <c r="D92">
@@ -10274,7 +10206,7 @@
       <c r="B93">
         <v>12</v>
       </c>
-      <c r="C93" s="4" t="s">
+      <c r="C93" t="s">
         <v>34</v>
       </c>
       <c r="D93">
@@ -10291,7 +10223,7 @@
       <c r="B94">
         <v>12</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="C94" t="s">
         <v>35</v>
       </c>
       <c r="D94">
@@ -10308,7 +10240,7 @@
       <c r="B95">
         <v>12</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="C95" t="s">
         <v>36</v>
       </c>
       <c r="D95">
@@ -10325,7 +10257,7 @@
       <c r="B96">
         <v>1</v>
       </c>
-      <c r="C96" s="4" t="s">
+      <c r="C96" t="s">
         <v>31</v>
       </c>
       <c r="D96">
@@ -10342,7 +10274,7 @@
       <c r="B97">
         <v>1</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="C97" t="s">
         <v>32</v>
       </c>
       <c r="D97">
@@ -10359,7 +10291,7 @@
       <c r="B98">
         <v>1</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C98" t="s">
         <v>33</v>
       </c>
       <c r="D98">
@@ -10376,7 +10308,7 @@
       <c r="B99">
         <v>1</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="C99" t="s">
         <v>34</v>
       </c>
       <c r="D99">
@@ -10393,7 +10325,7 @@
       <c r="B100">
         <v>1</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C100" t="s">
         <v>35</v>
       </c>
       <c r="D100">
@@ -10410,7 +10342,7 @@
       <c r="B101">
         <v>1</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="C101" t="s">
         <v>36</v>
       </c>
       <c r="D101">
@@ -10427,7 +10359,7 @@
       <c r="B102">
         <v>2</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="C102" t="s">
         <v>31</v>
       </c>
       <c r="D102">
@@ -10444,7 +10376,7 @@
       <c r="B103">
         <v>2</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="C103" t="s">
         <v>32</v>
       </c>
       <c r="D103">
@@ -10461,7 +10393,7 @@
       <c r="B104">
         <v>2</v>
       </c>
-      <c r="C104" s="4" t="s">
+      <c r="C104" t="s">
         <v>33</v>
       </c>
       <c r="D104">
@@ -10478,7 +10410,7 @@
       <c r="B105">
         <v>2</v>
       </c>
-      <c r="C105" s="4" t="s">
+      <c r="C105" t="s">
         <v>34</v>
       </c>
       <c r="D105">
@@ -10495,7 +10427,7 @@
       <c r="B106">
         <v>2</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="C106" t="s">
         <v>35</v>
       </c>
       <c r="D106">
@@ -10512,7 +10444,7 @@
       <c r="B107">
         <v>2</v>
       </c>
-      <c r="C107" s="4" t="s">
+      <c r="C107" t="s">
         <v>36</v>
       </c>
       <c r="D107">
@@ -10529,7 +10461,7 @@
       <c r="B108">
         <v>3</v>
       </c>
-      <c r="C108" s="4" t="s">
+      <c r="C108" t="s">
         <v>31</v>
       </c>
       <c r="D108">
@@ -10546,7 +10478,7 @@
       <c r="B109">
         <v>3</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="C109" t="s">
         <v>32</v>
       </c>
       <c r="D109">
@@ -10563,7 +10495,7 @@
       <c r="B110">
         <v>3</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="C110" t="s">
         <v>33</v>
       </c>
       <c r="D110">
@@ -10580,7 +10512,7 @@
       <c r="B111">
         <v>3</v>
       </c>
-      <c r="C111" s="4" t="s">
+      <c r="C111" t="s">
         <v>34</v>
       </c>
       <c r="D111">
@@ -10597,7 +10529,7 @@
       <c r="B112">
         <v>3</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="C112" t="s">
         <v>35</v>
       </c>
       <c r="D112">
@@ -10614,7 +10546,7 @@
       <c r="B113">
         <v>3</v>
       </c>
-      <c r="C113" s="4" t="s">
+      <c r="C113" t="s">
         <v>36</v>
       </c>
       <c r="D113">
@@ -10631,7 +10563,7 @@
       <c r="B114">
         <v>4</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="C114" t="s">
         <v>31</v>
       </c>
       <c r="D114">
@@ -10648,7 +10580,7 @@
       <c r="B115">
         <v>4</v>
       </c>
-      <c r="C115" s="4" t="s">
+      <c r="C115" t="s">
         <v>32</v>
       </c>
       <c r="D115">
@@ -10665,7 +10597,7 @@
       <c r="B116">
         <v>4</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C116" t="s">
         <v>33</v>
       </c>
       <c r="D116">
@@ -10682,7 +10614,7 @@
       <c r="B117">
         <v>4</v>
       </c>
-      <c r="C117" s="4" t="s">
+      <c r="C117" t="s">
         <v>34</v>
       </c>
       <c r="D117">
@@ -10699,7 +10631,7 @@
       <c r="B118">
         <v>4</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="C118" t="s">
         <v>35</v>
       </c>
       <c r="D118">
@@ -10716,7 +10648,7 @@
       <c r="B119">
         <v>4</v>
       </c>
-      <c r="C119" s="4" t="s">
+      <c r="C119" t="s">
         <v>36</v>
       </c>
       <c r="D119">
@@ -10733,7 +10665,7 @@
       <c r="B120">
         <v>5</v>
       </c>
-      <c r="C120" s="4" t="s">
+      <c r="C120" t="s">
         <v>31</v>
       </c>
       <c r="D120">
@@ -10750,7 +10682,7 @@
       <c r="B121">
         <v>5</v>
       </c>
-      <c r="C121" s="4" t="s">
+      <c r="C121" t="s">
         <v>32</v>
       </c>
       <c r="D121">
@@ -10767,7 +10699,7 @@
       <c r="B122">
         <v>5</v>
       </c>
-      <c r="C122" s="4" t="s">
+      <c r="C122" t="s">
         <v>33</v>
       </c>
       <c r="D122">
@@ -10784,7 +10716,7 @@
       <c r="B123">
         <v>5</v>
       </c>
-      <c r="C123" s="4" t="s">
+      <c r="C123" t="s">
         <v>34</v>
       </c>
       <c r="D123">
@@ -10801,7 +10733,7 @@
       <c r="B124">
         <v>5</v>
       </c>
-      <c r="C124" s="4" t="s">
+      <c r="C124" t="s">
         <v>35</v>
       </c>
       <c r="D124">
@@ -10818,7 +10750,7 @@
       <c r="B125">
         <v>5</v>
       </c>
-      <c r="C125" s="4" t="s">
+      <c r="C125" t="s">
         <v>36</v>
       </c>
       <c r="D125">
@@ -10835,7 +10767,7 @@
       <c r="B126">
         <v>6</v>
       </c>
-      <c r="C126" s="4" t="s">
+      <c r="C126" t="s">
         <v>31</v>
       </c>
       <c r="D126">
@@ -10852,7 +10784,7 @@
       <c r="B127">
         <v>6</v>
       </c>
-      <c r="C127" s="4" t="s">
+      <c r="C127" t="s">
         <v>32</v>
       </c>
       <c r="D127">
@@ -10869,7 +10801,7 @@
       <c r="B128">
         <v>6</v>
       </c>
-      <c r="C128" s="4" t="s">
+      <c r="C128" t="s">
         <v>33</v>
       </c>
       <c r="D128">
@@ -10886,7 +10818,7 @@
       <c r="B129">
         <v>6</v>
       </c>
-      <c r="C129" s="4" t="s">
+      <c r="C129" t="s">
         <v>34</v>
       </c>
       <c r="D129">
@@ -10903,7 +10835,7 @@
       <c r="B130">
         <v>6</v>
       </c>
-      <c r="C130" s="4" t="s">
+      <c r="C130" t="s">
         <v>35</v>
       </c>
       <c r="D130">
@@ -10920,7 +10852,7 @@
       <c r="B131">
         <v>6</v>
       </c>
-      <c r="C131" s="4" t="s">
+      <c r="C131" t="s">
         <v>36</v>
       </c>
       <c r="D131">
@@ -10937,7 +10869,7 @@
       <c r="B132">
         <v>7</v>
       </c>
-      <c r="C132" s="4" t="s">
+      <c r="C132" t="s">
         <v>31</v>
       </c>
       <c r="D132">
@@ -10954,7 +10886,7 @@
       <c r="B133">
         <v>7</v>
       </c>
-      <c r="C133" s="4" t="s">
+      <c r="C133" t="s">
         <v>32</v>
       </c>
       <c r="D133">
@@ -10971,7 +10903,7 @@
       <c r="B134">
         <v>7</v>
       </c>
-      <c r="C134" s="4" t="s">
+      <c r="C134" t="s">
         <v>33</v>
       </c>
       <c r="D134">
@@ -10988,7 +10920,7 @@
       <c r="B135">
         <v>7</v>
       </c>
-      <c r="C135" s="4" t="s">
+      <c r="C135" t="s">
         <v>34</v>
       </c>
       <c r="D135">
@@ -11005,7 +10937,7 @@
       <c r="B136">
         <v>7</v>
       </c>
-      <c r="C136" s="4" t="s">
+      <c r="C136" t="s">
         <v>35</v>
       </c>
       <c r="D136">
@@ -11022,7 +10954,7 @@
       <c r="B137">
         <v>7</v>
       </c>
-      <c r="C137" s="4" t="s">
+      <c r="C137" t="s">
         <v>36</v>
       </c>
       <c r="D137">
@@ -11039,7 +10971,7 @@
       <c r="B138">
         <v>8</v>
       </c>
-      <c r="C138" s="4" t="s">
+      <c r="C138" t="s">
         <v>31</v>
       </c>
       <c r="D138">
@@ -11056,7 +10988,7 @@
       <c r="B139">
         <v>8</v>
       </c>
-      <c r="C139" s="4" t="s">
+      <c r="C139" t="s">
         <v>32</v>
       </c>
       <c r="D139">
@@ -11073,7 +11005,7 @@
       <c r="B140">
         <v>8</v>
       </c>
-      <c r="C140" s="4" t="s">
+      <c r="C140" t="s">
         <v>33</v>
       </c>
       <c r="D140">
@@ -11090,7 +11022,7 @@
       <c r="B141">
         <v>8</v>
       </c>
-      <c r="C141" s="4" t="s">
+      <c r="C141" t="s">
         <v>34</v>
       </c>
       <c r="D141">
@@ -11107,7 +11039,7 @@
       <c r="B142">
         <v>8</v>
       </c>
-      <c r="C142" s="4" t="s">
+      <c r="C142" t="s">
         <v>35</v>
       </c>
       <c r="D142">
@@ -11124,7 +11056,7 @@
       <c r="B143">
         <v>8</v>
       </c>
-      <c r="C143" s="4" t="s">
+      <c r="C143" t="s">
         <v>36</v>
       </c>
       <c r="D143">
@@ -11141,7 +11073,7 @@
       <c r="B144">
         <v>9</v>
       </c>
-      <c r="C144" s="4" t="s">
+      <c r="C144" t="s">
         <v>31</v>
       </c>
       <c r="D144">
@@ -11158,7 +11090,7 @@
       <c r="B145">
         <v>9</v>
       </c>
-      <c r="C145" s="4" t="s">
+      <c r="C145" t="s">
         <v>32</v>
       </c>
       <c r="D145">
@@ -11175,7 +11107,7 @@
       <c r="B146">
         <v>9</v>
       </c>
-      <c r="C146" s="4" t="s">
+      <c r="C146" t="s">
         <v>33</v>
       </c>
       <c r="D146">
@@ -11192,7 +11124,7 @@
       <c r="B147">
         <v>9</v>
       </c>
-      <c r="C147" s="4" t="s">
+      <c r="C147" t="s">
         <v>34</v>
       </c>
       <c r="D147">
@@ -11209,7 +11141,7 @@
       <c r="B148">
         <v>9</v>
       </c>
-      <c r="C148" s="4" t="s">
+      <c r="C148" t="s">
         <v>35</v>
       </c>
       <c r="D148">
@@ -11226,7 +11158,7 @@
       <c r="B149">
         <v>9</v>
       </c>
-      <c r="C149" s="4" t="s">
+      <c r="C149" t="s">
         <v>36</v>
       </c>
       <c r="D149">
@@ -11243,7 +11175,7 @@
       <c r="B150">
         <v>10</v>
       </c>
-      <c r="C150" s="4" t="s">
+      <c r="C150" t="s">
         <v>31</v>
       </c>
       <c r="D150">
@@ -11260,7 +11192,7 @@
       <c r="B151">
         <v>10</v>
       </c>
-      <c r="C151" s="4" t="s">
+      <c r="C151" t="s">
         <v>32</v>
       </c>
       <c r="D151">
@@ -11277,7 +11209,7 @@
       <c r="B152">
         <v>10</v>
       </c>
-      <c r="C152" s="4" t="s">
+      <c r="C152" t="s">
         <v>33</v>
       </c>
       <c r="D152">
@@ -11294,7 +11226,7 @@
       <c r="B153">
         <v>10</v>
       </c>
-      <c r="C153" s="4" t="s">
+      <c r="C153" t="s">
         <v>34</v>
       </c>
       <c r="D153">
@@ -11311,7 +11243,7 @@
       <c r="B154">
         <v>10</v>
       </c>
-      <c r="C154" s="4" t="s">
+      <c r="C154" t="s">
         <v>35</v>
       </c>
       <c r="D154">
@@ -11328,7 +11260,7 @@
       <c r="B155">
         <v>10</v>
       </c>
-      <c r="C155" s="4" t="s">
+      <c r="C155" t="s">
         <v>36</v>
       </c>
       <c r="D155">
@@ -11345,7 +11277,7 @@
       <c r="B156">
         <v>11</v>
       </c>
-      <c r="C156" s="4" t="s">
+      <c r="C156" t="s">
         <v>31</v>
       </c>
       <c r="D156">
@@ -11362,7 +11294,7 @@
       <c r="B157">
         <v>11</v>
       </c>
-      <c r="C157" s="4" t="s">
+      <c r="C157" t="s">
         <v>32</v>
       </c>
       <c r="D157">
@@ -11379,7 +11311,7 @@
       <c r="B158">
         <v>11</v>
       </c>
-      <c r="C158" s="4" t="s">
+      <c r="C158" t="s">
         <v>33</v>
       </c>
       <c r="D158">
@@ -11396,7 +11328,7 @@
       <c r="B159">
         <v>11</v>
       </c>
-      <c r="C159" s="4" t="s">
+      <c r="C159" t="s">
         <v>34</v>
       </c>
       <c r="D159">
@@ -11413,7 +11345,7 @@
       <c r="B160">
         <v>11</v>
       </c>
-      <c r="C160" s="4" t="s">
+      <c r="C160" t="s">
         <v>35</v>
       </c>
       <c r="D160">
@@ -11430,7 +11362,7 @@
       <c r="B161">
         <v>11</v>
       </c>
-      <c r="C161" s="4" t="s">
+      <c r="C161" t="s">
         <v>36</v>
       </c>
       <c r="D161">
@@ -11447,7 +11379,7 @@
       <c r="B162">
         <v>12</v>
       </c>
-      <c r="C162" s="4" t="s">
+      <c r="C162" t="s">
         <v>31</v>
       </c>
       <c r="D162">
@@ -11464,7 +11396,7 @@
       <c r="B163">
         <v>12</v>
       </c>
-      <c r="C163" s="4" t="s">
+      <c r="C163" t="s">
         <v>32</v>
       </c>
       <c r="D163">
@@ -11481,7 +11413,7 @@
       <c r="B164">
         <v>12</v>
       </c>
-      <c r="C164" s="4" t="s">
+      <c r="C164" t="s">
         <v>33</v>
       </c>
       <c r="D164">
@@ -11498,7 +11430,7 @@
       <c r="B165">
         <v>12</v>
       </c>
-      <c r="C165" s="4" t="s">
+      <c r="C165" t="s">
         <v>34</v>
       </c>
       <c r="D165">
@@ -11515,7 +11447,7 @@
       <c r="B166">
         <v>12</v>
       </c>
-      <c r="C166" s="4" t="s">
+      <c r="C166" t="s">
         <v>35</v>
       </c>
       <c r="D166">
@@ -11532,7 +11464,7 @@
       <c r="B167">
         <v>12</v>
       </c>
-      <c r="C167" s="4" t="s">
+      <c r="C167" t="s">
         <v>36</v>
       </c>
       <c r="D167">
@@ -11549,7 +11481,7 @@
       <c r="B168">
         <v>1</v>
       </c>
-      <c r="C168" s="4" t="s">
+      <c r="C168" t="s">
         <v>31</v>
       </c>
       <c r="D168">
@@ -11566,7 +11498,7 @@
       <c r="B169">
         <v>1</v>
       </c>
-      <c r="C169" s="4" t="s">
+      <c r="C169" t="s">
         <v>32</v>
       </c>
       <c r="D169">
@@ -11583,7 +11515,7 @@
       <c r="B170">
         <v>1</v>
       </c>
-      <c r="C170" s="4" t="s">
+      <c r="C170" t="s">
         <v>33</v>
       </c>
       <c r="D170">
@@ -11600,7 +11532,7 @@
       <c r="B171">
         <v>1</v>
       </c>
-      <c r="C171" s="4" t="s">
+      <c r="C171" t="s">
         <v>34</v>
       </c>
       <c r="D171">
@@ -11617,7 +11549,7 @@
       <c r="B172">
         <v>1</v>
       </c>
-      <c r="C172" s="4" t="s">
+      <c r="C172" t="s">
         <v>35</v>
       </c>
       <c r="D172">
@@ -11634,7 +11566,7 @@
       <c r="B173">
         <v>1</v>
       </c>
-      <c r="C173" s="4" t="s">
+      <c r="C173" t="s">
         <v>36</v>
       </c>
       <c r="D173">
@@ -11651,7 +11583,7 @@
       <c r="B174">
         <v>2</v>
       </c>
-      <c r="C174" s="4" t="s">
+      <c r="C174" t="s">
         <v>31</v>
       </c>
       <c r="D174">
@@ -11668,7 +11600,7 @@
       <c r="B175">
         <v>2</v>
       </c>
-      <c r="C175" s="4" t="s">
+      <c r="C175" t="s">
         <v>32</v>
       </c>
       <c r="D175">
@@ -11685,7 +11617,7 @@
       <c r="B176">
         <v>2</v>
       </c>
-      <c r="C176" s="4" t="s">
+      <c r="C176" t="s">
         <v>33</v>
       </c>
       <c r="D176">
@@ -11702,7 +11634,7 @@
       <c r="B177">
         <v>2</v>
       </c>
-      <c r="C177" s="4" t="s">
+      <c r="C177" t="s">
         <v>34</v>
       </c>
       <c r="D177">
@@ -11719,7 +11651,7 @@
       <c r="B178">
         <v>2</v>
       </c>
-      <c r="C178" s="4" t="s">
+      <c r="C178" t="s">
         <v>35</v>
       </c>
       <c r="D178">
@@ -11736,7 +11668,7 @@
       <c r="B179">
         <v>2</v>
       </c>
-      <c r="C179" s="4" t="s">
+      <c r="C179" t="s">
         <v>36</v>
       </c>
       <c r="D179">
@@ -11753,7 +11685,7 @@
       <c r="B180">
         <v>3</v>
       </c>
-      <c r="C180" s="4" t="s">
+      <c r="C180" t="s">
         <v>31</v>
       </c>
       <c r="D180">
@@ -11770,7 +11702,7 @@
       <c r="B181">
         <v>3</v>
       </c>
-      <c r="C181" s="4" t="s">
+      <c r="C181" t="s">
         <v>32</v>
       </c>
       <c r="D181">
@@ -11787,7 +11719,7 @@
       <c r="B182">
         <v>3</v>
       </c>
-      <c r="C182" s="4" t="s">
+      <c r="C182" t="s">
         <v>33</v>
       </c>
       <c r="D182">
@@ -11804,7 +11736,7 @@
       <c r="B183">
         <v>3</v>
       </c>
-      <c r="C183" s="4" t="s">
+      <c r="C183" t="s">
         <v>34</v>
       </c>
       <c r="D183">
@@ -11821,7 +11753,7 @@
       <c r="B184">
         <v>3</v>
       </c>
-      <c r="C184" s="4" t="s">
+      <c r="C184" t="s">
         <v>35</v>
       </c>
       <c r="D184">
@@ -11838,7 +11770,7 @@
       <c r="B185">
         <v>3</v>
       </c>
-      <c r="C185" s="4" t="s">
+      <c r="C185" t="s">
         <v>36</v>
       </c>
       <c r="D185">
@@ -11855,7 +11787,7 @@
       <c r="B186">
         <v>4</v>
       </c>
-      <c r="C186" s="4" t="s">
+      <c r="C186" t="s">
         <v>31</v>
       </c>
       <c r="D186">
@@ -11872,7 +11804,7 @@
       <c r="B187">
         <v>4</v>
       </c>
-      <c r="C187" s="4" t="s">
+      <c r="C187" t="s">
         <v>32</v>
       </c>
       <c r="D187">
@@ -11889,7 +11821,7 @@
       <c r="B188">
         <v>4</v>
       </c>
-      <c r="C188" s="4" t="s">
+      <c r="C188" t="s">
         <v>33</v>
       </c>
       <c r="D188">
@@ -11906,7 +11838,7 @@
       <c r="B189">
         <v>4</v>
       </c>
-      <c r="C189" s="4" t="s">
+      <c r="C189" t="s">
         <v>34</v>
       </c>
       <c r="D189">
@@ -11923,7 +11855,7 @@
       <c r="B190">
         <v>4</v>
       </c>
-      <c r="C190" s="4" t="s">
+      <c r="C190" t="s">
         <v>35</v>
       </c>
       <c r="D190">
@@ -11940,7 +11872,7 @@
       <c r="B191">
         <v>4</v>
       </c>
-      <c r="C191" s="4" t="s">
+      <c r="C191" t="s">
         <v>36</v>
       </c>
       <c r="D191">
@@ -11957,7 +11889,7 @@
       <c r="B192">
         <v>5</v>
       </c>
-      <c r="C192" s="4" t="s">
+      <c r="C192" t="s">
         <v>31</v>
       </c>
       <c r="D192">
@@ -11974,7 +11906,7 @@
       <c r="B193">
         <v>5</v>
       </c>
-      <c r="C193" s="4" t="s">
+      <c r="C193" t="s">
         <v>32</v>
       </c>
       <c r="D193">
@@ -11991,7 +11923,7 @@
       <c r="B194">
         <v>5</v>
       </c>
-      <c r="C194" s="4" t="s">
+      <c r="C194" t="s">
         <v>33</v>
       </c>
       <c r="D194">
@@ -12008,7 +11940,7 @@
       <c r="B195">
         <v>5</v>
       </c>
-      <c r="C195" s="4" t="s">
+      <c r="C195" t="s">
         <v>34</v>
       </c>
       <c r="D195">
@@ -12025,7 +11957,7 @@
       <c r="B196">
         <v>5</v>
       </c>
-      <c r="C196" s="4" t="s">
+      <c r="C196" t="s">
         <v>35</v>
       </c>
       <c r="D196">
@@ -12042,7 +11974,7 @@
       <c r="B197">
         <v>5</v>
       </c>
-      <c r="C197" s="4" t="s">
+      <c r="C197" t="s">
         <v>36</v>
       </c>
       <c r="D197">
@@ -12059,7 +11991,7 @@
       <c r="B198">
         <v>6</v>
       </c>
-      <c r="C198" s="4" t="s">
+      <c r="C198" t="s">
         <v>31</v>
       </c>
       <c r="D198">
@@ -12076,7 +12008,7 @@
       <c r="B199">
         <v>6</v>
       </c>
-      <c r="C199" s="4" t="s">
+      <c r="C199" t="s">
         <v>32</v>
       </c>
       <c r="D199">
@@ -12093,7 +12025,7 @@
       <c r="B200">
         <v>6</v>
       </c>
-      <c r="C200" s="4" t="s">
+      <c r="C200" t="s">
         <v>33</v>
       </c>
       <c r="D200">
@@ -12110,7 +12042,7 @@
       <c r="B201">
         <v>6</v>
       </c>
-      <c r="C201" s="4" t="s">
+      <c r="C201" t="s">
         <v>34</v>
       </c>
       <c r="D201">
@@ -12127,7 +12059,7 @@
       <c r="B202">
         <v>6</v>
       </c>
-      <c r="C202" s="4" t="s">
+      <c r="C202" t="s">
         <v>35</v>
       </c>
       <c r="D202">
@@ -12144,7 +12076,7 @@
       <c r="B203">
         <v>6</v>
       </c>
-      <c r="C203" s="4" t="s">
+      <c r="C203" t="s">
         <v>36</v>
       </c>
       <c r="D203">
@@ -12161,7 +12093,7 @@
       <c r="B204">
         <v>7</v>
       </c>
-      <c r="C204" s="4" t="s">
+      <c r="C204" t="s">
         <v>31</v>
       </c>
       <c r="D204">
@@ -12178,7 +12110,7 @@
       <c r="B205">
         <v>7</v>
       </c>
-      <c r="C205" s="4" t="s">
+      <c r="C205" t="s">
         <v>32</v>
       </c>
       <c r="D205">
@@ -12195,7 +12127,7 @@
       <c r="B206">
         <v>7</v>
       </c>
-      <c r="C206" s="4" t="s">
+      <c r="C206" t="s">
         <v>33</v>
       </c>
       <c r="D206">
@@ -12212,7 +12144,7 @@
       <c r="B207">
         <v>7</v>
       </c>
-      <c r="C207" s="4" t="s">
+      <c r="C207" t="s">
         <v>34</v>
       </c>
       <c r="D207">
@@ -12229,7 +12161,7 @@
       <c r="B208">
         <v>7</v>
       </c>
-      <c r="C208" s="4" t="s">
+      <c r="C208" t="s">
         <v>35</v>
       </c>
       <c r="D208">
@@ -12246,7 +12178,7 @@
       <c r="B209">
         <v>7</v>
       </c>
-      <c r="C209" s="4" t="s">
+      <c r="C209" t="s">
         <v>36</v>
       </c>
       <c r="D209">
@@ -12263,7 +12195,7 @@
       <c r="B210">
         <v>8</v>
       </c>
-      <c r="C210" s="4" t="s">
+      <c r="C210" t="s">
         <v>31</v>
       </c>
       <c r="D210">
@@ -12280,7 +12212,7 @@
       <c r="B211">
         <v>8</v>
       </c>
-      <c r="C211" s="4" t="s">
+      <c r="C211" t="s">
         <v>32</v>
       </c>
       <c r="D211">
@@ -12297,7 +12229,7 @@
       <c r="B212">
         <v>8</v>
       </c>
-      <c r="C212" s="4" t="s">
+      <c r="C212" t="s">
         <v>33</v>
       </c>
       <c r="D212">
@@ -12314,7 +12246,7 @@
       <c r="B213">
         <v>8</v>
       </c>
-      <c r="C213" s="4" t="s">
+      <c r="C213" t="s">
         <v>34</v>
       </c>
       <c r="D213">
@@ -12331,7 +12263,7 @@
       <c r="B214">
         <v>8</v>
       </c>
-      <c r="C214" s="4" t="s">
+      <c r="C214" t="s">
         <v>35</v>
       </c>
       <c r="D214">
@@ -12348,7 +12280,7 @@
       <c r="B215">
         <v>8</v>
       </c>
-      <c r="C215" s="4" t="s">
+      <c r="C215" t="s">
         <v>36</v>
       </c>
       <c r="D215">
@@ -12365,7 +12297,7 @@
       <c r="B216">
         <v>9</v>
       </c>
-      <c r="C216" s="4" t="s">
+      <c r="C216" t="s">
         <v>31</v>
       </c>
       <c r="D216">
@@ -12382,7 +12314,7 @@
       <c r="B217">
         <v>9</v>
       </c>
-      <c r="C217" s="4" t="s">
+      <c r="C217" t="s">
         <v>32</v>
       </c>
       <c r="D217">
@@ -12399,7 +12331,7 @@
       <c r="B218">
         <v>9</v>
       </c>
-      <c r="C218" s="4" t="s">
+      <c r="C218" t="s">
         <v>33</v>
       </c>
       <c r="D218">
@@ -12416,7 +12348,7 @@
       <c r="B219">
         <v>9</v>
       </c>
-      <c r="C219" s="4" t="s">
+      <c r="C219" t="s">
         <v>34</v>
       </c>
       <c r="D219">
@@ -12433,7 +12365,7 @@
       <c r="B220">
         <v>9</v>
       </c>
-      <c r="C220" s="4" t="s">
+      <c r="C220" t="s">
         <v>35</v>
       </c>
       <c r="D220">
@@ -12450,7 +12382,7 @@
       <c r="B221">
         <v>9</v>
       </c>
-      <c r="C221" s="4" t="s">
+      <c r="C221" t="s">
         <v>36</v>
       </c>
       <c r="D221">
@@ -12467,7 +12399,7 @@
       <c r="B222">
         <v>10</v>
       </c>
-      <c r="C222" s="4" t="s">
+      <c r="C222" t="s">
         <v>31</v>
       </c>
       <c r="D222">
@@ -12484,7 +12416,7 @@
       <c r="B223">
         <v>10</v>
       </c>
-      <c r="C223" s="4" t="s">
+      <c r="C223" t="s">
         <v>32</v>
       </c>
       <c r="D223">
@@ -12501,7 +12433,7 @@
       <c r="B224">
         <v>10</v>
       </c>
-      <c r="C224" s="4" t="s">
+      <c r="C224" t="s">
         <v>33</v>
       </c>
       <c r="D224">
@@ -12518,7 +12450,7 @@
       <c r="B225">
         <v>10</v>
       </c>
-      <c r="C225" s="4" t="s">
+      <c r="C225" t="s">
         <v>34</v>
       </c>
       <c r="D225">
@@ -12535,7 +12467,7 @@
       <c r="B226">
         <v>10</v>
       </c>
-      <c r="C226" s="4" t="s">
+      <c r="C226" t="s">
         <v>35</v>
       </c>
       <c r="D226">
@@ -12552,7 +12484,7 @@
       <c r="B227">
         <v>10</v>
       </c>
-      <c r="C227" s="4" t="s">
+      <c r="C227" t="s">
         <v>36</v>
       </c>
       <c r="D227">
@@ -12569,7 +12501,7 @@
       <c r="B228">
         <v>11</v>
       </c>
-      <c r="C228" s="4" t="s">
+      <c r="C228" t="s">
         <v>31</v>
       </c>
       <c r="D228">
@@ -12586,7 +12518,7 @@
       <c r="B229">
         <v>11</v>
       </c>
-      <c r="C229" s="4" t="s">
+      <c r="C229" t="s">
         <v>32</v>
       </c>
       <c r="D229">
@@ -12603,7 +12535,7 @@
       <c r="B230">
         <v>11</v>
       </c>
-      <c r="C230" s="4" t="s">
+      <c r="C230" t="s">
         <v>33</v>
       </c>
       <c r="D230">
@@ -12620,7 +12552,7 @@
       <c r="B231">
         <v>11</v>
       </c>
-      <c r="C231" s="4" t="s">
+      <c r="C231" t="s">
         <v>34</v>
       </c>
       <c r="D231">
@@ -12637,7 +12569,7 @@
       <c r="B232">
         <v>11</v>
       </c>
-      <c r="C232" s="4" t="s">
+      <c r="C232" t="s">
         <v>35</v>
       </c>
       <c r="D232">
@@ -12654,7 +12586,7 @@
       <c r="B233">
         <v>11</v>
       </c>
-      <c r="C233" s="4" t="s">
+      <c r="C233" t="s">
         <v>36</v>
       </c>
       <c r="D233">
@@ -12671,7 +12603,7 @@
       <c r="B234">
         <v>12</v>
       </c>
-      <c r="C234" s="4" t="s">
+      <c r="C234" t="s">
         <v>31</v>
       </c>
       <c r="D234">
@@ -12688,7 +12620,7 @@
       <c r="B235">
         <v>12</v>
       </c>
-      <c r="C235" s="4" t="s">
+      <c r="C235" t="s">
         <v>32</v>
       </c>
       <c r="D235">
@@ -12705,7 +12637,7 @@
       <c r="B236">
         <v>12</v>
       </c>
-      <c r="C236" s="4" t="s">
+      <c r="C236" t="s">
         <v>33</v>
       </c>
       <c r="D236">
@@ -12722,7 +12654,7 @@
       <c r="B237">
         <v>12</v>
       </c>
-      <c r="C237" s="4" t="s">
+      <c r="C237" t="s">
         <v>34</v>
       </c>
       <c r="D237">
@@ -12739,7 +12671,7 @@
       <c r="B238">
         <v>12</v>
       </c>
-      <c r="C238" s="4" t="s">
+      <c r="C238" t="s">
         <v>35</v>
       </c>
       <c r="D238">
@@ -12756,7 +12688,7 @@
       <c r="B239">
         <v>12</v>
       </c>
-      <c r="C239" s="4" t="s">
+      <c r="C239" t="s">
         <v>36</v>
       </c>
       <c r="D239">
@@ -12773,7 +12705,7 @@
       <c r="B240">
         <v>1</v>
       </c>
-      <c r="C240" s="4" t="s">
+      <c r="C240" t="s">
         <v>31</v>
       </c>
       <c r="D240">
@@ -12790,7 +12722,7 @@
       <c r="B241">
         <v>1</v>
       </c>
-      <c r="C241" s="4" t="s">
+      <c r="C241" t="s">
         <v>32</v>
       </c>
       <c r="D241">
@@ -12807,7 +12739,7 @@
       <c r="B242">
         <v>1</v>
       </c>
-      <c r="C242" s="4" t="s">
+      <c r="C242" t="s">
         <v>33</v>
       </c>
       <c r="D242">
@@ -12824,7 +12756,7 @@
       <c r="B243">
         <v>1</v>
       </c>
-      <c r="C243" s="4" t="s">
+      <c r="C243" t="s">
         <v>34</v>
       </c>
       <c r="D243">
@@ -12841,7 +12773,7 @@
       <c r="B244">
         <v>1</v>
       </c>
-      <c r="C244" s="4" t="s">
+      <c r="C244" t="s">
         <v>35</v>
       </c>
       <c r="D244">
@@ -12858,7 +12790,7 @@
       <c r="B245">
         <v>1</v>
       </c>
-      <c r="C245" s="4" t="s">
+      <c r="C245" t="s">
         <v>36</v>
       </c>
       <c r="D245">
@@ -12875,7 +12807,7 @@
       <c r="B246">
         <v>2</v>
       </c>
-      <c r="C246" s="4" t="s">
+      <c r="C246" t="s">
         <v>31</v>
       </c>
       <c r="D246">
@@ -12892,7 +12824,7 @@
       <c r="B247">
         <v>2</v>
       </c>
-      <c r="C247" s="4" t="s">
+      <c r="C247" t="s">
         <v>32</v>
       </c>
       <c r="D247">
@@ -12909,7 +12841,7 @@
       <c r="B248">
         <v>2</v>
       </c>
-      <c r="C248" s="4" t="s">
+      <c r="C248" t="s">
         <v>33</v>
       </c>
       <c r="D248">
@@ -12926,7 +12858,7 @@
       <c r="B249">
         <v>2</v>
       </c>
-      <c r="C249" s="4" t="s">
+      <c r="C249" t="s">
         <v>34</v>
       </c>
       <c r="D249">
@@ -12943,7 +12875,7 @@
       <c r="B250">
         <v>2</v>
       </c>
-      <c r="C250" s="4" t="s">
+      <c r="C250" t="s">
         <v>35</v>
       </c>
       <c r="D250">
@@ -12960,7 +12892,7 @@
       <c r="B251">
         <v>2</v>
       </c>
-      <c r="C251" s="4" t="s">
+      <c r="C251" t="s">
         <v>36</v>
       </c>
       <c r="D251">
@@ -12977,7 +12909,7 @@
       <c r="B252">
         <v>3</v>
       </c>
-      <c r="C252" s="4" t="s">
+      <c r="C252" t="s">
         <v>31</v>
       </c>
       <c r="D252">
@@ -12994,7 +12926,7 @@
       <c r="B253">
         <v>3</v>
       </c>
-      <c r="C253" s="4" t="s">
+      <c r="C253" t="s">
         <v>32</v>
       </c>
       <c r="D253">
@@ -13011,7 +12943,7 @@
       <c r="B254">
         <v>3</v>
       </c>
-      <c r="C254" s="4" t="s">
+      <c r="C254" t="s">
         <v>33</v>
       </c>
       <c r="D254">
@@ -13028,7 +12960,7 @@
       <c r="B255">
         <v>3</v>
       </c>
-      <c r="C255" s="4" t="s">
+      <c r="C255" t="s">
         <v>34</v>
       </c>
       <c r="D255">
@@ -13045,7 +12977,7 @@
       <c r="B256">
         <v>3</v>
       </c>
-      <c r="C256" s="4" t="s">
+      <c r="C256" t="s">
         <v>35</v>
       </c>
       <c r="D256">
@@ -13062,7 +12994,7 @@
       <c r="B257">
         <v>3</v>
       </c>
-      <c r="C257" s="4" t="s">
+      <c r="C257" t="s">
         <v>36</v>
       </c>
       <c r="D257">
@@ -13079,7 +13011,7 @@
       <c r="B258">
         <v>4</v>
       </c>
-      <c r="C258" s="4" t="s">
+      <c r="C258" t="s">
         <v>31</v>
       </c>
       <c r="D258">
@@ -13096,7 +13028,7 @@
       <c r="B259">
         <v>4</v>
       </c>
-      <c r="C259" s="4" t="s">
+      <c r="C259" t="s">
         <v>32</v>
       </c>
       <c r="D259">
@@ -13113,7 +13045,7 @@
       <c r="B260">
         <v>4</v>
       </c>
-      <c r="C260" s="4" t="s">
+      <c r="C260" t="s">
         <v>33</v>
       </c>
       <c r="D260">
@@ -13130,7 +13062,7 @@
       <c r="B261">
         <v>4</v>
       </c>
-      <c r="C261" s="4" t="s">
+      <c r="C261" t="s">
         <v>34</v>
       </c>
       <c r="D261">
@@ -13147,7 +13079,7 @@
       <c r="B262">
         <v>4</v>
       </c>
-      <c r="C262" s="4" t="s">
+      <c r="C262" t="s">
         <v>35</v>
       </c>
       <c r="D262">
@@ -13164,7 +13096,7 @@
       <c r="B263">
         <v>4</v>
       </c>
-      <c r="C263" s="4" t="s">
+      <c r="C263" t="s">
         <v>36</v>
       </c>
       <c r="D263">
@@ -13181,7 +13113,7 @@
       <c r="B264">
         <v>5</v>
       </c>
-      <c r="C264" s="4" t="s">
+      <c r="C264" t="s">
         <v>31</v>
       </c>
       <c r="D264">
@@ -13198,7 +13130,7 @@
       <c r="B265">
         <v>5</v>
       </c>
-      <c r="C265" s="4" t="s">
+      <c r="C265" t="s">
         <v>32</v>
       </c>
       <c r="D265">
@@ -13215,7 +13147,7 @@
       <c r="B266">
         <v>5</v>
       </c>
-      <c r="C266" s="4" t="s">
+      <c r="C266" t="s">
         <v>33</v>
       </c>
       <c r="D266">
@@ -13232,7 +13164,7 @@
       <c r="B267">
         <v>5</v>
       </c>
-      <c r="C267" s="4" t="s">
+      <c r="C267" t="s">
         <v>34</v>
       </c>
       <c r="D267">
@@ -13249,7 +13181,7 @@
       <c r="B268">
         <v>5</v>
       </c>
-      <c r="C268" s="4" t="s">
+      <c r="C268" t="s">
         <v>35</v>
       </c>
       <c r="D268">
@@ -13266,7 +13198,7 @@
       <c r="B269">
         <v>5</v>
       </c>
-      <c r="C269" s="4" t="s">
+      <c r="C269" t="s">
         <v>36</v>
       </c>
       <c r="D269">
@@ -13283,7 +13215,7 @@
       <c r="B270">
         <v>6</v>
       </c>
-      <c r="C270" s="4" t="s">
+      <c r="C270" t="s">
         <v>31</v>
       </c>
       <c r="D270">
@@ -13300,7 +13232,7 @@
       <c r="B271">
         <v>6</v>
       </c>
-      <c r="C271" s="4" t="s">
+      <c r="C271" t="s">
         <v>32</v>
       </c>
       <c r="D271">
@@ -13317,7 +13249,7 @@
       <c r="B272">
         <v>6</v>
       </c>
-      <c r="C272" s="4" t="s">
+      <c r="C272" t="s">
         <v>33</v>
       </c>
       <c r="D272">
@@ -13334,7 +13266,7 @@
       <c r="B273">
         <v>6</v>
       </c>
-      <c r="C273" s="4" t="s">
+      <c r="C273" t="s">
         <v>34</v>
       </c>
       <c r="D273">
@@ -13351,7 +13283,7 @@
       <c r="B274">
         <v>6</v>
       </c>
-      <c r="C274" s="4" t="s">
+      <c r="C274" t="s">
         <v>35</v>
       </c>
       <c r="D274">
@@ -13368,7 +13300,7 @@
       <c r="B275">
         <v>6</v>
       </c>
-      <c r="C275" s="4" t="s">
+      <c r="C275" t="s">
         <v>36</v>
       </c>
       <c r="D275">
@@ -13385,7 +13317,7 @@
       <c r="B276">
         <v>7</v>
       </c>
-      <c r="C276" s="4" t="s">
+      <c r="C276" t="s">
         <v>31</v>
       </c>
       <c r="D276">
@@ -13402,7 +13334,7 @@
       <c r="B277">
         <v>7</v>
       </c>
-      <c r="C277" s="4" t="s">
+      <c r="C277" t="s">
         <v>32</v>
       </c>
       <c r="D277">
@@ -13419,7 +13351,7 @@
       <c r="B278">
         <v>7</v>
       </c>
-      <c r="C278" s="4" t="s">
+      <c r="C278" t="s">
         <v>33</v>
       </c>
       <c r="D278">
@@ -13436,7 +13368,7 @@
       <c r="B279">
         <v>7</v>
       </c>
-      <c r="C279" s="4" t="s">
+      <c r="C279" t="s">
         <v>34</v>
       </c>
       <c r="D279">
@@ -13453,7 +13385,7 @@
       <c r="B280">
         <v>7</v>
       </c>
-      <c r="C280" s="4" t="s">
+      <c r="C280" t="s">
         <v>35</v>
       </c>
       <c r="D280">
@@ -13470,7 +13402,7 @@
       <c r="B281">
         <v>7</v>
       </c>
-      <c r="C281" s="4" t="s">
+      <c r="C281" t="s">
         <v>36</v>
       </c>
       <c r="D281">
@@ -13487,7 +13419,7 @@
       <c r="B282">
         <v>8</v>
       </c>
-      <c r="C282" s="4" t="s">
+      <c r="C282" t="s">
         <v>31</v>
       </c>
       <c r="D282">
@@ -13504,7 +13436,7 @@
       <c r="B283">
         <v>8</v>
       </c>
-      <c r="C283" s="4" t="s">
+      <c r="C283" t="s">
         <v>32</v>
       </c>
       <c r="D283">
@@ -13521,7 +13453,7 @@
       <c r="B284">
         <v>8</v>
       </c>
-      <c r="C284" s="4" t="s">
+      <c r="C284" t="s">
         <v>33</v>
       </c>
       <c r="D284">
@@ -13538,7 +13470,7 @@
       <c r="B285">
         <v>8</v>
       </c>
-      <c r="C285" s="4" t="s">
+      <c r="C285" t="s">
         <v>34</v>
       </c>
       <c r="D285">
@@ -13555,7 +13487,7 @@
       <c r="B286">
         <v>8</v>
       </c>
-      <c r="C286" s="4" t="s">
+      <c r="C286" t="s">
         <v>35</v>
       </c>
       <c r="D286">
@@ -13572,7 +13504,7 @@
       <c r="B287">
         <v>8</v>
       </c>
-      <c r="C287" s="4" t="s">
+      <c r="C287" t="s">
         <v>36</v>
       </c>
       <c r="D287">
@@ -13589,7 +13521,7 @@
       <c r="B288">
         <v>9</v>
       </c>
-      <c r="C288" s="4" t="s">
+      <c r="C288" t="s">
         <v>31</v>
       </c>
       <c r="D288">
@@ -13606,7 +13538,7 @@
       <c r="B289">
         <v>9</v>
       </c>
-      <c r="C289" s="4" t="s">
+      <c r="C289" t="s">
         <v>32</v>
       </c>
       <c r="D289">
@@ -13623,7 +13555,7 @@
       <c r="B290">
         <v>9</v>
       </c>
-      <c r="C290" s="4" t="s">
+      <c r="C290" t="s">
         <v>33</v>
       </c>
       <c r="D290">
@@ -13640,7 +13572,7 @@
       <c r="B291">
         <v>9</v>
       </c>
-      <c r="C291" s="4" t="s">
+      <c r="C291" t="s">
         <v>34</v>
       </c>
       <c r="D291">
@@ -13657,7 +13589,7 @@
       <c r="B292">
         <v>9</v>
       </c>
-      <c r="C292" s="4" t="s">
+      <c r="C292" t="s">
         <v>35</v>
       </c>
       <c r="D292">
@@ -13674,7 +13606,7 @@
       <c r="B293">
         <v>9</v>
       </c>
-      <c r="C293" s="4" t="s">
+      <c r="C293" t="s">
         <v>36</v>
       </c>
       <c r="D293">
@@ -13691,7 +13623,7 @@
       <c r="B294">
         <v>10</v>
       </c>
-      <c r="C294" s="4" t="s">
+      <c r="C294" t="s">
         <v>31</v>
       </c>
       <c r="D294">
@@ -13708,7 +13640,7 @@
       <c r="B295">
         <v>10</v>
       </c>
-      <c r="C295" s="4" t="s">
+      <c r="C295" t="s">
         <v>32</v>
       </c>
       <c r="D295">
@@ -13725,7 +13657,7 @@
       <c r="B296">
         <v>10</v>
       </c>
-      <c r="C296" s="4" t="s">
+      <c r="C296" t="s">
         <v>33</v>
       </c>
       <c r="D296">
@@ -13742,7 +13674,7 @@
       <c r="B297">
         <v>10</v>
       </c>
-      <c r="C297" s="4" t="s">
+      <c r="C297" t="s">
         <v>34</v>
       </c>
       <c r="D297">
@@ -13759,7 +13691,7 @@
       <c r="B298">
         <v>10</v>
       </c>
-      <c r="C298" s="4" t="s">
+      <c r="C298" t="s">
         <v>35</v>
       </c>
       <c r="D298">
@@ -13776,7 +13708,7 @@
       <c r="B299">
         <v>10</v>
       </c>
-      <c r="C299" s="4" t="s">
+      <c r="C299" t="s">
         <v>36</v>
       </c>
       <c r="D299">
@@ -13793,7 +13725,7 @@
       <c r="B300">
         <v>11</v>
       </c>
-      <c r="C300" s="4" t="s">
+      <c r="C300" t="s">
         <v>31</v>
       </c>
       <c r="D300">
@@ -13810,7 +13742,7 @@
       <c r="B301">
         <v>11</v>
       </c>
-      <c r="C301" s="4" t="s">
+      <c r="C301" t="s">
         <v>32</v>
       </c>
       <c r="D301">
@@ -13827,7 +13759,7 @@
       <c r="B302">
         <v>11</v>
       </c>
-      <c r="C302" s="4" t="s">
+      <c r="C302" t="s">
         <v>33</v>
       </c>
       <c r="D302">
@@ -13844,7 +13776,7 @@
       <c r="B303">
         <v>11</v>
       </c>
-      <c r="C303" s="4" t="s">
+      <c r="C303" t="s">
         <v>34</v>
       </c>
       <c r="D303">
@@ -13861,7 +13793,7 @@
       <c r="B304">
         <v>11</v>
       </c>
-      <c r="C304" s="4" t="s">
+      <c r="C304" t="s">
         <v>35</v>
       </c>
       <c r="D304">
@@ -13878,7 +13810,7 @@
       <c r="B305">
         <v>11</v>
       </c>
-      <c r="C305" s="4" t="s">
+      <c r="C305" t="s">
         <v>36</v>
       </c>
       <c r="D305">
@@ -13895,7 +13827,7 @@
       <c r="B306">
         <v>12</v>
       </c>
-      <c r="C306" s="4" t="s">
+      <c r="C306" t="s">
         <v>31</v>
       </c>
       <c r="D306">
@@ -13912,7 +13844,7 @@
       <c r="B307">
         <v>12</v>
       </c>
-      <c r="C307" s="4" t="s">
+      <c r="C307" t="s">
         <v>32</v>
       </c>
       <c r="D307">
@@ -13929,7 +13861,7 @@
       <c r="B308">
         <v>12</v>
       </c>
-      <c r="C308" s="4" t="s">
+      <c r="C308" t="s">
         <v>33</v>
       </c>
       <c r="D308">
@@ -13946,7 +13878,7 @@
       <c r="B309">
         <v>12</v>
       </c>
-      <c r="C309" s="4" t="s">
+      <c r="C309" t="s">
         <v>34</v>
       </c>
       <c r="D309">
@@ -13963,7 +13895,7 @@
       <c r="B310">
         <v>12</v>
       </c>
-      <c r="C310" s="4" t="s">
+      <c r="C310" t="s">
         <v>35</v>
       </c>
       <c r="D310">
@@ -13980,7 +13912,7 @@
       <c r="B311">
         <v>12</v>
       </c>
-      <c r="C311" s="4" t="s">
+      <c r="C311" t="s">
         <v>36</v>
       </c>
       <c r="D311">
@@ -14022,7 +13954,7 @@
       <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>0.70057470007317668</v>
       </c>
     </row>
@@ -14030,7 +13962,7 @@
       <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>0.29942529992682343</v>
       </c>
     </row>
@@ -14038,7 +13970,7 @@
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>1</v>
       </c>
     </row>
@@ -14054,7 +13986,7 @@
       <c r="A26" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="4">
         <v>1.5929326869437436E-2</v>
       </c>
     </row>
@@ -14062,7 +13994,7 @@
       <c r="A27" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="4">
         <v>7.8805283793012326E-2</v>
       </c>
     </row>
@@ -14070,7 +14002,7 @@
       <c r="A28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="4">
         <v>8.213184872907868E-2</v>
       </c>
     </row>
@@ -14078,7 +14010,7 @@
       <c r="A29" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="4">
         <v>8.5183667846208386E-2</v>
       </c>
     </row>
@@ -14086,7 +14018,7 @@
       <c r="A30" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="4">
         <v>8.5722746505192599E-2</v>
       </c>
     </row>
@@ -14094,7 +14026,7 @@
       <c r="A31" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31" s="4">
         <v>8.7221922883620059E-2</v>
       </c>
     </row>
@@ -14102,7 +14034,7 @@
       <c r="A32" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32" s="4">
         <v>8.7237052277785582E-2</v>
       </c>
     </row>
@@ -14110,7 +14042,7 @@
       <c r="A33" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33" s="4">
         <v>9.1469277202132118E-2</v>
       </c>
     </row>
@@ -14118,7 +14050,7 @@
       <c r="A34" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="4">
         <v>9.6762619492480315E-2</v>
       </c>
     </row>
@@ -14126,7 +14058,7 @@
       <c r="A35" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35" s="4">
         <v>0.10292218469821034</v>
       </c>
     </row>
@@ -14134,7 +14066,7 @@
       <c r="A36" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="4">
         <v>0.18661406970284225</v>
       </c>
     </row>
@@ -14142,7 +14074,7 @@
       <c r="A37" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37" s="4">
         <v>1</v>
       </c>
     </row>
@@ -14158,7 +14090,7 @@
       <c r="A48" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48">
         <v>465.94915349999997</v>
       </c>
     </row>
@@ -14166,7 +14098,7 @@
       <c r="A49" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B49" s="4">
+      <c r="B49">
         <v>174.62502535416672</v>
       </c>
     </row>
@@ -14174,7 +14106,7 @@
       <c r="A50" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50">
         <v>32.343998083333339</v>
       </c>
     </row>
@@ -14182,7 +14114,7 @@
       <c r="A51" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B51" s="4">
+      <c r="B51">
         <v>31.639881937500007</v>
       </c>
     </row>
@@ -14190,7 +14122,7 @@
       <c r="A52" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52">
         <v>29.195210708333331</v>
       </c>
     </row>
@@ -14198,7 +14130,7 @@
       <c r="A53" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B53" s="4">
+      <c r="B53">
         <v>10.105105000000002</v>
       </c>
     </row>
@@ -14206,7 +14138,7 @@
       <c r="A54" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54">
         <v>123.9763957638889</v>
       </c>
     </row>
@@ -14794,7 +14726,7 @@
       <c r="A2" s="2">
         <v>2022</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2">
         <v>579864.30999999994</v>
       </c>
     </row>
@@ -14802,7 +14734,7 @@
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3">
         <v>40857.199999999997</v>
       </c>
     </row>
@@ -14810,7 +14742,7 @@
       <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>52729.22</v>
       </c>
     </row>
@@ -14818,7 +14750,7 @@
       <c r="A5" s="3">
         <v>3</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>49214.95</v>
       </c>
     </row>
@@ -14826,7 +14758,7 @@
       <c r="A6" s="3">
         <v>4</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>55229.25</v>
       </c>
     </row>
@@ -14834,7 +14766,7 @@
       <c r="A7" s="3">
         <v>5</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <v>49696.98</v>
       </c>
     </row>
@@ -14842,7 +14774,7 @@
       <c r="A8" s="3">
         <v>6</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8">
         <v>45208.26</v>
       </c>
     </row>
@@ -14850,7 +14782,7 @@
       <c r="A9" s="3">
         <v>7</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9">
         <v>48308.66</v>
       </c>
     </row>
@@ -14858,7 +14790,7 @@
       <c r="A10" s="3">
         <v>8</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10">
         <v>49641.33</v>
       </c>
     </row>
@@ -14866,7 +14798,7 @@
       <c r="A11" s="3">
         <v>9</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11">
         <v>47977.04</v>
       </c>
     </row>
@@ -14874,7 +14806,7 @@
       <c r="A12" s="3">
         <v>10</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12">
         <v>50543.1</v>
       </c>
     </row>
@@ -14882,7 +14814,7 @@
       <c r="A13" s="3">
         <v>11</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13">
         <v>41402.480000000003</v>
       </c>
     </row>
@@ -14890,7 +14822,7 @@
       <c r="A14" s="3">
         <v>12</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14">
         <v>49055.839999999997</v>
       </c>
     </row>
@@ -14898,7 +14830,7 @@
       <c r="A15" s="2">
         <v>2023</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15">
         <v>807866.79</v>
       </c>
     </row>
@@ -14906,7 +14838,7 @@
       <c r="A16" s="3">
         <v>1</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16">
         <v>72298.63</v>
       </c>
     </row>
@@ -14914,7 +14846,7 @@
       <c r="A17" s="3">
         <v>2</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17">
         <v>45399.37</v>
       </c>
     </row>
@@ -14922,7 +14854,7 @@
       <c r="A18" s="3">
         <v>3</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18">
         <v>67468.759999999995</v>
       </c>
     </row>
@@ -14930,7 +14862,7 @@
       <c r="A19" s="3">
         <v>4</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19">
         <v>76712.34</v>
       </c>
     </row>
@@ -14938,7 +14870,7 @@
       <c r="A20" s="3">
         <v>5</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20">
         <v>74059.48</v>
       </c>
     </row>
@@ -14946,7 +14878,7 @@
       <c r="A21" s="3">
         <v>6</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21">
         <v>68340.039999999994</v>
       </c>
     </row>
@@ -14954,7 +14886,7 @@
       <c r="A22" s="3">
         <v>7</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22">
         <v>63941.07</v>
       </c>
     </row>
@@ -14962,7 +14894,7 @@
       <c r="A23" s="3">
         <v>8</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23">
         <v>60700.57</v>
       </c>
     </row>
@@ -14970,7 +14902,7 @@
       <c r="A24" s="3">
         <v>9</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24">
         <v>69674.13</v>
       </c>
     </row>
@@ -14978,7 +14910,7 @@
       <c r="A25" s="3">
         <v>10</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25">
         <v>64725.08</v>
       </c>
     </row>
@@ -14986,7 +14918,7 @@
       <c r="A26" s="3">
         <v>11</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26">
         <v>65553.06</v>
       </c>
     </row>
@@ -14994,7 +14926,7 @@
       <c r="A27" s="3">
         <v>12</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27">
         <v>78994.259999999995</v>
       </c>
     </row>
@@ -15002,7 +14934,7 @@
       <c r="A28" s="2">
         <v>2024</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28">
         <v>809371.87</v>
       </c>
     </row>
@@ -15010,7 +14942,7 @@
       <c r="A29" s="3">
         <v>1</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29">
         <v>49824.160000000003</v>
       </c>
     </row>
@@ -15018,7 +14950,7 @@
       <c r="A30" s="3">
         <v>2</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30">
         <v>64549.05</v>
       </c>
     </row>
@@ -15026,7 +14958,7 @@
       <c r="A31" s="3">
         <v>3</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31">
         <v>80723.94</v>
       </c>
     </row>
@@ -15034,7 +14966,7 @@
       <c r="A32" s="3">
         <v>4</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32">
         <v>70047.88</v>
       </c>
     </row>
@@ -15042,7 +14974,7 @@
       <c r="A33" s="3">
         <v>5</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33">
         <v>70733.08</v>
       </c>
     </row>
@@ -15050,7 +14982,7 @@
       <c r="A34" s="3">
         <v>6</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34">
         <v>61548.03</v>
       </c>
     </row>
@@ -15058,7 +14990,7 @@
       <c r="A35" s="3">
         <v>7</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35">
         <v>60700.57</v>
       </c>
     </row>
@@ -15066,7 +14998,7 @@
       <c r="A36" s="3">
         <v>8</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36">
         <v>71514.05</v>
       </c>
     </row>
@@ -15074,7 +15006,7 @@
       <c r="A37" s="3">
         <v>9</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37">
         <v>62885.16</v>
       </c>
     </row>
@@ -15082,7 +15014,7 @@
       <c r="A38" s="3">
         <v>10</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38">
         <v>70341.95</v>
       </c>
     </row>
@@ -15090,7 +15022,7 @@
       <c r="A39" s="3">
         <v>11</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B39">
         <v>74205.37</v>
       </c>
     </row>
@@ -15098,7 +15030,7 @@
       <c r="A40" s="3">
         <v>12</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B40">
         <v>72298.63</v>
       </c>
     </row>
@@ -15106,7 +15038,7 @@
       <c r="A41" s="2">
         <v>2025</v>
       </c>
-      <c r="B41" s="4">
+      <c r="B41">
         <v>1220747.0399999998</v>
       </c>
     </row>
@@ -15114,7 +15046,7 @@
       <c r="A42" s="3">
         <v>1</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B42">
         <v>101046.12</v>
       </c>
     </row>
@@ -15122,7 +15054,7 @@
       <c r="A43" s="3">
         <v>2</v>
       </c>
-      <c r="B43" s="4">
+      <c r="B43">
         <v>95007.06</v>
       </c>
     </row>
@@ -15130,7 +15062,7 @@
       <c r="A44" s="3">
         <v>3</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B44">
         <v>101490.54</v>
       </c>
     </row>
@@ -15138,7 +15070,7 @@
       <c r="A45" s="3">
         <v>4</v>
       </c>
-      <c r="B45" s="4">
+      <c r="B45">
         <v>81348.63</v>
       </c>
     </row>
@@ -15146,7 +15078,7 @@
       <c r="A46" s="3">
         <v>5</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B46">
         <v>85801.23</v>
       </c>
     </row>
@@ -15154,7 +15086,7 @@
       <c r="A47" s="3">
         <v>6</v>
       </c>
-      <c r="B47" s="4">
+      <c r="B47">
         <v>87182.86</v>
       </c>
     </row>
@@ -15162,7 +15094,7 @@
       <c r="A48" s="3">
         <v>7</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48">
         <v>91246.68</v>
       </c>
     </row>
@@ -15170,7 +15102,7 @@
       <c r="A49" s="3">
         <v>8</v>
       </c>
-      <c r="B49" s="4">
+      <c r="B49">
         <v>98630.93</v>
       </c>
     </row>
@@ -15178,7 +15110,7 @@
       <c r="A50" s="3">
         <v>9</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50">
         <v>109065.94</v>
       </c>
     </row>
@@ -15186,7 +15118,7 @@
       <c r="A51" s="3">
         <v>10</v>
       </c>
-      <c r="B51" s="4">
+      <c r="B51">
         <v>168955.72</v>
       </c>
     </row>
@@ -15194,7 +15126,7 @@
       <c r="A52" s="3">
         <v>11</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52">
         <v>105400.74</v>
       </c>
     </row>
@@ -15202,7 +15134,7 @@
       <c r="A53" s="3">
         <v>12</v>
       </c>
-      <c r="B53" s="4">
+      <c r="B53">
         <v>95570.59</v>
       </c>
     </row>
@@ -15210,7 +15142,7 @@
       <c r="A54" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54">
         <v>3417850.0100000002</v>
       </c>
     </row>

--- a/Chanthadara_territory_chart.xlsx
+++ b/Chanthadara_territory_chart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chimm\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8581C3D3-C9FE-4795-B4F7-EB785FA774EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C7B0D09-7659-4CD1-8EA3-3FBDCC20A2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{4F9622DB-3F0B-4399-96EC-3CBDB6BB25F8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4F9622DB-3F0B-4399-96EC-3CBDB6BB25F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Findings" sheetId="7" r:id="rId1"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="40">
   <si>
     <t>Year</t>
   </si>
@@ -86,9 +86,6 @@
   </si>
   <si>
     <t>Total_Revenue</t>
-  </si>
-  <si>
-    <t>Row Labels</t>
   </si>
   <si>
     <t>Grand Total</t>
@@ -193,7 +190,13 @@
     <t>TexasAvgSale</t>
   </si>
   <si>
-    <t>Average of Avg_Transaction</t>
+    <t>Categories</t>
+  </si>
+  <si>
+    <t>Average Transactions</t>
+  </si>
+  <si>
+    <t>Year&amp;Months</t>
   </si>
 </sst>
 </file>
@@ -431,7 +434,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Findings_Chart!$B$25</c:f>
+              <c:f>Findings_Chart!$B$24</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -529,7 +532,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Findings_Chart!$A$26:$A$37</c:f>
+              <c:f>Findings_Chart!$A$25:$A$36</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -570,7 +573,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Findings_Chart!$B$26:$B$37</c:f>
+              <c:f>Findings_Chart!$B$25:$B$36</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="11"/>
@@ -1311,6 +1314,15 @@
             <c:idx val="0"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000003-48F8-4410-BCF9-56C98C67EEB2}"/>
@@ -1321,6 +1333,15 @@
             <c:idx val="1"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000004-48F8-4410-BCF9-56C98C67EEB2}"/>
@@ -1800,6 +1821,31 @@
   </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Transactions</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1899,7 +1945,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Findings_Chart!$B$47</c:f>
+              <c:f>Findings_Chart!$B$50</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1920,7 +1966,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Findings_Chart!$A$48:$A$54</c:f>
+              <c:f>Findings_Chart!$A$51:$A$57</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -1946,7 +1992,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Findings_Chart!$B$48:$B$54</c:f>
+              <c:f>Findings_Chart!$B$51:$B$57</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -1997,6 +2043,61 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Categories</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2076,6 +2177,66 @@
             <a:effectLst/>
           </c:spPr>
         </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Average</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Transactions</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -5229,9 +5390,9 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>594360</xdr:colOff>
+      <xdr:colOff>518160</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>175260</xdr:rowOff>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
@@ -5306,10 +5467,10 @@
       <xdr:rowOff>3810</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5341,16 +5502,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>601980</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7886,98 +8047,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6B0FE92-A8F0-44F2-81AE-8F660C0D359C}" name="PivotTable7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="A47:B54" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Avg_Transaction" fld="4" subtotal="average" baseField="2" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CD5EED47-6634-433F-8246-8166C77A8301}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6" rowHeaderCaption="Territory">
   <location ref="A7:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
@@ -8057,9 +8126,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4F5F414B-C686-4F7F-BA97-F099CE7B7DB1}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18" rowHeaderCaption="Store Location">
-  <location ref="A25:B37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A24:B36" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField showAll="0">
       <items count="12">
@@ -8189,8 +8258,100 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6B0FE92-A8F0-44F2-81AE-8F660C0D359C}" name="PivotTable7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Categories">
+  <location ref="A50:B57" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average Transactions" fld="4" subtotal="average" baseField="2" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6BFC6F99-E6B7-4784-8CBE-342B2F900FC9}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6BFC6F99-E6B7-4784-8CBE-342B2F900FC9}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12" rowHeaderCaption="Year&amp;Months">
   <location ref="A1:B54" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -8840,12 +9001,12 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -8853,7 +9014,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3">
         <v>3417850.01</v>
@@ -8861,7 +9022,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>7996850.1200000001</v>
@@ -8869,15 +9030,15 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
         <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
       </c>
       <c r="C8" t="s">
         <v>2</v>
@@ -8888,7 +9049,7 @@
         <v>905</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9">
         <v>637818.9</v>
@@ -8899,7 +9060,7 @@
         <v>910</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10">
         <v>351772.59</v>
@@ -8910,7 +9071,7 @@
         <v>909</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11">
         <v>330720.12</v>
@@ -8921,7 +9082,7 @@
         <v>906</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12">
         <v>312628.27</v>
@@ -8932,7 +9093,7 @@
         <v>904</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13">
         <v>298163.15999999997</v>
@@ -8943,7 +9104,7 @@
         <v>908</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14">
         <v>298111.45</v>
@@ -8954,7 +9115,7 @@
         <v>901</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15">
         <v>292987.49</v>
@@ -8965,7 +9126,7 @@
         <v>902</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16">
         <v>291145</v>
@@ -8976,7 +9137,7 @@
         <v>903</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17">
         <v>280714.34000000003</v>
@@ -8987,7 +9148,7 @@
         <v>911</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18">
         <v>269344.64000000001</v>
@@ -8998,7 +9159,7 @@
         <v>907</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19">
         <v>54444.05</v>
@@ -9006,7 +9167,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -9017,13 +9178,13 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" t="s">
         <v>28</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>29</v>
-      </c>
-      <c r="E23" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -9034,7 +9195,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D24">
         <v>55</v>
@@ -9051,7 +9212,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D25">
         <v>44</v>
@@ -9068,7 +9229,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D26">
         <v>28</v>
@@ -9085,7 +9246,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D27">
         <v>69</v>
@@ -9102,7 +9263,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D28">
         <v>69</v>
@@ -9119,7 +9280,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D29">
         <v>56</v>
@@ -9136,7 +9297,7 @@
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D30">
         <v>66</v>
@@ -9153,7 +9314,7 @@
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D31">
         <v>49</v>
@@ -9170,7 +9331,7 @@
         <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D32">
         <v>23</v>
@@ -9187,7 +9348,7 @@
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D33">
         <v>50</v>
@@ -9204,7 +9365,7 @@
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D34">
         <v>80</v>
@@ -9221,7 +9382,7 @@
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D35">
         <v>56</v>
@@ -9238,7 +9399,7 @@
         <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D36">
         <v>50</v>
@@ -9255,7 +9416,7 @@
         <v>3</v>
       </c>
       <c r="C37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D37">
         <v>42</v>
@@ -9272,7 +9433,7 @@
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D38">
         <v>29</v>
@@ -9289,7 +9450,7 @@
         <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D39">
         <v>63</v>
@@ -9306,7 +9467,7 @@
         <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D40">
         <v>63</v>
@@ -9323,7 +9484,7 @@
         <v>3</v>
       </c>
       <c r="C41" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D41">
         <v>60</v>
@@ -9340,7 +9501,7 @@
         <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D42">
         <v>35</v>
@@ -9357,7 +9518,7 @@
         <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D43">
         <v>51</v>
@@ -9374,7 +9535,7 @@
         <v>4</v>
       </c>
       <c r="C44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D44">
         <v>31</v>
@@ -9391,7 +9552,7 @@
         <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D45">
         <v>64</v>
@@ -9408,7 +9569,7 @@
         <v>4</v>
       </c>
       <c r="C46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D46">
         <v>82</v>
@@ -9425,7 +9586,7 @@
         <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D47">
         <v>58</v>
@@ -9442,7 +9603,7 @@
         <v>5</v>
       </c>
       <c r="C48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D48">
         <v>55</v>
@@ -9459,7 +9620,7 @@
         <v>5</v>
       </c>
       <c r="C49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D49">
         <v>47</v>
@@ -9476,7 +9637,7 @@
         <v>5</v>
       </c>
       <c r="C50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D50">
         <v>26</v>
@@ -9493,7 +9654,7 @@
         <v>5</v>
       </c>
       <c r="C51" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D51">
         <v>55</v>
@@ -9510,7 +9671,7 @@
         <v>5</v>
       </c>
       <c r="C52" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D52">
         <v>79</v>
@@ -9527,7 +9688,7 @@
         <v>5</v>
       </c>
       <c r="C53" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D53">
         <v>76</v>
@@ -9544,7 +9705,7 @@
         <v>6</v>
       </c>
       <c r="C54" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D54">
         <v>62</v>
@@ -9561,7 +9722,7 @@
         <v>6</v>
       </c>
       <c r="C55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D55">
         <v>55</v>
@@ -9578,7 +9739,7 @@
         <v>6</v>
       </c>
       <c r="C56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D56">
         <v>26</v>
@@ -9595,7 +9756,7 @@
         <v>6</v>
       </c>
       <c r="C57" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D57">
         <v>76</v>
@@ -9612,7 +9773,7 @@
         <v>6</v>
       </c>
       <c r="C58" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -9629,7 +9790,7 @@
         <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D59">
         <v>47</v>
@@ -9646,7 +9807,7 @@
         <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D60">
         <v>48</v>
@@ -9663,7 +9824,7 @@
         <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D61">
         <v>49</v>
@@ -9680,7 +9841,7 @@
         <v>7</v>
       </c>
       <c r="C62" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D62">
         <v>26</v>
@@ -9697,7 +9858,7 @@
         <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D63">
         <v>77</v>
@@ -9714,7 +9875,7 @@
         <v>7</v>
       </c>
       <c r="C64" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D64">
         <v>66</v>
@@ -9731,7 +9892,7 @@
         <v>7</v>
       </c>
       <c r="C65" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D65">
         <v>73</v>
@@ -9748,7 +9909,7 @@
         <v>8</v>
       </c>
       <c r="C66" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D66">
         <v>57</v>
@@ -9765,7 +9926,7 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D67">
         <v>39</v>
@@ -9782,7 +9943,7 @@
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D68">
         <v>23</v>
@@ -9799,7 +9960,7 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D69">
         <v>69</v>
@@ -9816,7 +9977,7 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D70">
         <v>74</v>
@@ -9833,7 +9994,7 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D71">
         <v>60</v>
@@ -9850,7 +10011,7 @@
         <v>9</v>
       </c>
       <c r="C72" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D72">
         <v>59</v>
@@ -9867,7 +10028,7 @@
         <v>9</v>
       </c>
       <c r="C73" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D73">
         <v>52</v>
@@ -9884,7 +10045,7 @@
         <v>9</v>
       </c>
       <c r="C74" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D74">
         <v>28</v>
@@ -9901,7 +10062,7 @@
         <v>9</v>
       </c>
       <c r="C75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D75">
         <v>70</v>
@@ -9918,7 +10079,7 @@
         <v>9</v>
       </c>
       <c r="C76" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D76">
         <v>65</v>
@@ -9935,7 +10096,7 @@
         <v>9</v>
       </c>
       <c r="C77" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D77">
         <v>60</v>
@@ -9952,7 +10113,7 @@
         <v>10</v>
       </c>
       <c r="C78" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D78">
         <v>56</v>
@@ -9969,7 +10130,7 @@
         <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D79">
         <v>56</v>
@@ -9986,7 +10147,7 @@
         <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D80">
         <v>21</v>
@@ -10003,7 +10164,7 @@
         <v>10</v>
       </c>
       <c r="C81" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D81">
         <v>75</v>
@@ -10020,7 +10181,7 @@
         <v>10</v>
       </c>
       <c r="C82" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D82">
         <v>80</v>
@@ -10037,7 +10198,7 @@
         <v>10</v>
       </c>
       <c r="C83" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D83">
         <v>69</v>
@@ -10054,7 +10215,7 @@
         <v>11</v>
       </c>
       <c r="C84" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D84">
         <v>54</v>
@@ -10071,7 +10232,7 @@
         <v>11</v>
       </c>
       <c r="C85" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D85">
         <v>41</v>
@@ -10088,7 +10249,7 @@
         <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D86">
         <v>30</v>
@@ -10105,7 +10266,7 @@
         <v>11</v>
       </c>
       <c r="C87" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D87">
         <v>71</v>
@@ -10122,7 +10283,7 @@
         <v>11</v>
       </c>
       <c r="C88" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D88">
         <v>69</v>
@@ -10139,7 +10300,7 @@
         <v>11</v>
       </c>
       <c r="C89" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D89">
         <v>57</v>
@@ -10156,7 +10317,7 @@
         <v>12</v>
       </c>
       <c r="C90" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D90">
         <v>53</v>
@@ -10173,7 +10334,7 @@
         <v>12</v>
       </c>
       <c r="C91" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D91">
         <v>50</v>
@@ -10190,7 +10351,7 @@
         <v>12</v>
       </c>
       <c r="C92" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D92">
         <v>27</v>
@@ -10207,7 +10368,7 @@
         <v>12</v>
       </c>
       <c r="C93" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D93">
         <v>61</v>
@@ -10224,7 +10385,7 @@
         <v>12</v>
       </c>
       <c r="C94" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D94">
         <v>64</v>
@@ -10241,7 +10402,7 @@
         <v>12</v>
       </c>
       <c r="C95" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D95">
         <v>60</v>
@@ -10258,7 +10419,7 @@
         <v>1</v>
       </c>
       <c r="C96" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D96">
         <v>94</v>
@@ -10275,7 +10436,7 @@
         <v>1</v>
       </c>
       <c r="C97" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D97">
         <v>74</v>
@@ -10292,7 +10453,7 @@
         <v>1</v>
       </c>
       <c r="C98" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D98">
         <v>34</v>
@@ -10309,7 +10470,7 @@
         <v>1</v>
       </c>
       <c r="C99" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D99">
         <v>87</v>
@@ -10326,7 +10487,7 @@
         <v>1</v>
       </c>
       <c r="C100" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D100">
         <v>122</v>
@@ -10343,7 +10504,7 @@
         <v>1</v>
       </c>
       <c r="C101" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D101">
         <v>51</v>
@@ -10360,7 +10521,7 @@
         <v>2</v>
       </c>
       <c r="C102" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D102">
         <v>67</v>
@@ -10377,7 +10538,7 @@
         <v>2</v>
       </c>
       <c r="C103" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D103">
         <v>78</v>
@@ -10394,7 +10555,7 @@
         <v>2</v>
       </c>
       <c r="C104" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D104">
         <v>20</v>
@@ -10411,7 +10572,7 @@
         <v>2</v>
       </c>
       <c r="C105" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D105">
         <v>89</v>
@@ -10428,7 +10589,7 @@
         <v>2</v>
       </c>
       <c r="C106" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D106">
         <v>77</v>
@@ -10445,7 +10606,7 @@
         <v>2</v>
       </c>
       <c r="C107" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D107">
         <v>57</v>
@@ -10462,7 +10623,7 @@
         <v>3</v>
       </c>
       <c r="C108" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D108">
         <v>80</v>
@@ -10479,7 +10640,7 @@
         <v>3</v>
       </c>
       <c r="C109" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D109">
         <v>52</v>
@@ -10496,7 +10657,7 @@
         <v>3</v>
       </c>
       <c r="C110" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D110">
         <v>35</v>
@@ -10513,7 +10674,7 @@
         <v>3</v>
       </c>
       <c r="C111" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D111">
         <v>90</v>
@@ -10530,7 +10691,7 @@
         <v>3</v>
       </c>
       <c r="C112" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D112">
         <v>112</v>
@@ -10547,7 +10708,7 @@
         <v>3</v>
       </c>
       <c r="C113" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D113">
         <v>60</v>
@@ -10564,7 +10725,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D114">
         <v>72</v>
@@ -10581,7 +10742,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D115">
         <v>71</v>
@@ -10598,7 +10759,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D116">
         <v>32</v>
@@ -10615,7 +10776,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D117">
         <v>127</v>
@@ -10632,7 +10793,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D118">
         <v>128</v>
@@ -10649,7 +10810,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D119">
         <v>63</v>
@@ -10666,7 +10827,7 @@
         <v>5</v>
       </c>
       <c r="C120" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D120">
         <v>72</v>
@@ -10683,7 +10844,7 @@
         <v>5</v>
       </c>
       <c r="C121" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D121">
         <v>65</v>
@@ -10700,7 +10861,7 @@
         <v>5</v>
       </c>
       <c r="C122" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D122">
         <v>36</v>
@@ -10717,7 +10878,7 @@
         <v>5</v>
       </c>
       <c r="C123" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D123">
         <v>93</v>
@@ -10734,7 +10895,7 @@
         <v>5</v>
       </c>
       <c r="C124" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D124">
         <v>107</v>
@@ -10751,7 +10912,7 @@
         <v>5</v>
       </c>
       <c r="C125" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D125">
         <v>70</v>
@@ -10768,7 +10929,7 @@
         <v>6</v>
       </c>
       <c r="C126" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D126">
         <v>56</v>
@@ -10785,7 +10946,7 @@
         <v>6</v>
       </c>
       <c r="C127" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D127">
         <v>79</v>
@@ -10802,7 +10963,7 @@
         <v>6</v>
       </c>
       <c r="C128" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D128">
         <v>38</v>
@@ -10819,7 +10980,7 @@
         <v>6</v>
       </c>
       <c r="C129" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D129">
         <v>97</v>
@@ -10836,7 +10997,7 @@
         <v>6</v>
       </c>
       <c r="C130" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D130">
         <v>107</v>
@@ -10853,7 +11014,7 @@
         <v>6</v>
       </c>
       <c r="C131" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D131">
         <v>66</v>
@@ -10870,7 +11031,7 @@
         <v>7</v>
       </c>
       <c r="C132" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D132">
         <v>88</v>
@@ -10887,7 +11048,7 @@
         <v>7</v>
       </c>
       <c r="C133" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D133">
         <v>60</v>
@@ -10904,7 +11065,7 @@
         <v>7</v>
       </c>
       <c r="C134" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -10921,7 +11082,7 @@
         <v>7</v>
       </c>
       <c r="C135" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D135">
         <v>92</v>
@@ -10938,7 +11099,7 @@
         <v>7</v>
       </c>
       <c r="C136" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D136">
         <v>98</v>
@@ -10955,7 +11116,7 @@
         <v>7</v>
       </c>
       <c r="C137" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D137">
         <v>76</v>
@@ -10972,7 +11133,7 @@
         <v>8</v>
       </c>
       <c r="C138" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D138">
         <v>70</v>
@@ -10989,7 +11150,7 @@
         <v>8</v>
       </c>
       <c r="C139" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D139">
         <v>80</v>
@@ -11006,7 +11167,7 @@
         <v>8</v>
       </c>
       <c r="C140" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D140">
         <v>35</v>
@@ -11023,7 +11184,7 @@
         <v>8</v>
       </c>
       <c r="C141" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D141">
         <v>102</v>
@@ -11040,7 +11201,7 @@
         <v>8</v>
       </c>
       <c r="C142" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D142">
         <v>91</v>
@@ -11057,7 +11218,7 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D143">
         <v>77</v>
@@ -11074,7 +11235,7 @@
         <v>9</v>
       </c>
       <c r="C144" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D144">
         <v>70</v>
@@ -11091,7 +11252,7 @@
         <v>9</v>
       </c>
       <c r="C145" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D145">
         <v>58</v>
@@ -11108,7 +11269,7 @@
         <v>9</v>
       </c>
       <c r="C146" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D146">
         <v>29</v>
@@ -11125,7 +11286,7 @@
         <v>9</v>
       </c>
       <c r="C147" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D147">
         <v>87</v>
@@ -11142,7 +11303,7 @@
         <v>9</v>
       </c>
       <c r="C148" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D148">
         <v>104</v>
@@ -11159,7 +11320,7 @@
         <v>9</v>
       </c>
       <c r="C149" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D149">
         <v>75</v>
@@ -11176,7 +11337,7 @@
         <v>10</v>
       </c>
       <c r="C150" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D150">
         <v>94</v>
@@ -11193,7 +11354,7 @@
         <v>10</v>
       </c>
       <c r="C151" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D151">
         <v>69</v>
@@ -11210,7 +11371,7 @@
         <v>10</v>
       </c>
       <c r="C152" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D152">
         <v>44</v>
@@ -11227,7 +11388,7 @@
         <v>10</v>
       </c>
       <c r="C153" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D153">
         <v>74</v>
@@ -11244,7 +11405,7 @@
         <v>10</v>
       </c>
       <c r="C154" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D154">
         <v>91</v>
@@ -11261,7 +11422,7 @@
         <v>10</v>
       </c>
       <c r="C155" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D155">
         <v>86</v>
@@ -11278,7 +11439,7 @@
         <v>11</v>
       </c>
       <c r="C156" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D156">
         <v>78</v>
@@ -11295,7 +11456,7 @@
         <v>11</v>
       </c>
       <c r="C157" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D157">
         <v>59</v>
@@ -11312,7 +11473,7 @@
         <v>11</v>
       </c>
       <c r="C158" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D158">
         <v>40</v>
@@ -11329,7 +11490,7 @@
         <v>11</v>
       </c>
       <c r="C159" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D159">
         <v>89</v>
@@ -11346,7 +11507,7 @@
         <v>11</v>
       </c>
       <c r="C160" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D160">
         <v>103</v>
@@ -11363,7 +11524,7 @@
         <v>11</v>
       </c>
       <c r="C161" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D161">
         <v>89</v>
@@ -11380,7 +11541,7 @@
         <v>12</v>
       </c>
       <c r="C162" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D162">
         <v>83</v>
@@ -11397,7 +11558,7 @@
         <v>12</v>
       </c>
       <c r="C163" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D163">
         <v>79</v>
@@ -11414,7 +11575,7 @@
         <v>12</v>
       </c>
       <c r="C164" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D164">
         <v>25</v>
@@ -11431,7 +11592,7 @@
         <v>12</v>
       </c>
       <c r="C165" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D165">
         <v>102</v>
@@ -11448,7 +11609,7 @@
         <v>12</v>
       </c>
       <c r="C166" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D166">
         <v>115</v>
@@ -11465,7 +11626,7 @@
         <v>12</v>
       </c>
       <c r="C167" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D167">
         <v>91</v>
@@ -11482,7 +11643,7 @@
         <v>1</v>
       </c>
       <c r="C168" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D168">
         <v>73</v>
@@ -11499,7 +11660,7 @@
         <v>1</v>
       </c>
       <c r="C169" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D169">
         <v>86</v>
@@ -11516,7 +11677,7 @@
         <v>1</v>
       </c>
       <c r="C170" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D170">
         <v>23</v>
@@ -11533,7 +11694,7 @@
         <v>1</v>
       </c>
       <c r="C171" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D171">
         <v>96</v>
@@ -11550,7 +11711,7 @@
         <v>1</v>
       </c>
       <c r="C172" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D172">
         <v>88</v>
@@ -11567,7 +11728,7 @@
         <v>1</v>
       </c>
       <c r="C173" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D173">
         <v>63</v>
@@ -11584,7 +11745,7 @@
         <v>2</v>
       </c>
       <c r="C174" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -11601,7 +11762,7 @@
         <v>2</v>
       </c>
       <c r="C175" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D175">
         <v>46</v>
@@ -11618,7 +11779,7 @@
         <v>2</v>
       </c>
       <c r="C176" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D176">
         <v>33</v>
@@ -11635,7 +11796,7 @@
         <v>2</v>
       </c>
       <c r="C177" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D177">
         <v>85</v>
@@ -11652,7 +11813,7 @@
         <v>2</v>
       </c>
       <c r="C178" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D178">
         <v>103</v>
@@ -11669,7 +11830,7 @@
         <v>2</v>
       </c>
       <c r="C179" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D179">
         <v>56</v>
@@ -11686,7 +11847,7 @@
         <v>3</v>
       </c>
       <c r="C180" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D180">
         <v>74</v>
@@ -11703,7 +11864,7 @@
         <v>3</v>
       </c>
       <c r="C181" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D181">
         <v>73</v>
@@ -11720,7 +11881,7 @@
         <v>3</v>
       </c>
       <c r="C182" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D182">
         <v>33</v>
@@ -11737,7 +11898,7 @@
         <v>3</v>
       </c>
       <c r="C183" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D183">
         <v>128</v>
@@ -11754,7 +11915,7 @@
         <v>3</v>
       </c>
       <c r="C184" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D184">
         <v>133</v>
@@ -11771,7 +11932,7 @@
         <v>3</v>
       </c>
       <c r="C185" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D185">
         <v>68</v>
@@ -11788,7 +11949,7 @@
         <v>4</v>
       </c>
       <c r="C186" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D186">
         <v>70</v>
@@ -11805,7 +11966,7 @@
         <v>4</v>
       </c>
       <c r="C187" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D187">
         <v>63</v>
@@ -11822,7 +11983,7 @@
         <v>4</v>
       </c>
       <c r="C188" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D188">
         <v>35</v>
@@ -11839,7 +12000,7 @@
         <v>4</v>
       </c>
       <c r="C189" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D189">
         <v>92</v>
@@ -11856,7 +12017,7 @@
         <v>4</v>
       </c>
       <c r="C190" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D190">
         <v>102</v>
@@ -11873,7 +12034,7 @@
         <v>4</v>
       </c>
       <c r="C191" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D191">
         <v>65</v>
@@ -11890,7 +12051,7 @@
         <v>5</v>
       </c>
       <c r="C192" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D192">
         <v>58</v>
@@ -11907,7 +12068,7 @@
         <v>5</v>
       </c>
       <c r="C193" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D193">
         <v>81</v>
@@ -11924,7 +12085,7 @@
         <v>5</v>
       </c>
       <c r="C194" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D194">
         <v>38</v>
@@ -11941,7 +12102,7 @@
         <v>5</v>
       </c>
       <c r="C195" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D195">
         <v>99</v>
@@ -11958,7 +12119,7 @@
         <v>5</v>
       </c>
       <c r="C196" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D196">
         <v>111</v>
@@ -11975,7 +12136,7 @@
         <v>5</v>
       </c>
       <c r="C197" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D197">
         <v>70</v>
@@ -11992,7 +12153,7 @@
         <v>6</v>
       </c>
       <c r="C198" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D198">
         <v>86</v>
@@ -12009,7 +12170,7 @@
         <v>6</v>
       </c>
       <c r="C199" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D199">
         <v>58</v>
@@ -12026,7 +12187,7 @@
         <v>6</v>
       </c>
       <c r="C200" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D200">
         <v>37</v>
@@ -12043,7 +12204,7 @@
         <v>6</v>
       </c>
       <c r="C201" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D201">
         <v>90</v>
@@ -12060,7 +12221,7 @@
         <v>6</v>
       </c>
       <c r="C202" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D202">
         <v>94</v>
@@ -12077,7 +12238,7 @@
         <v>6</v>
       </c>
       <c r="C203" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D203">
         <v>72</v>
@@ -12094,7 +12255,7 @@
         <v>7</v>
       </c>
       <c r="C204" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D204">
         <v>70</v>
@@ -12111,7 +12272,7 @@
         <v>7</v>
       </c>
       <c r="C205" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D205">
         <v>80</v>
@@ -12128,7 +12289,7 @@
         <v>7</v>
       </c>
       <c r="C206" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D206">
         <v>35</v>
@@ -12145,7 +12306,7 @@
         <v>7</v>
       </c>
       <c r="C207" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D207">
         <v>102</v>
@@ -12162,7 +12323,7 @@
         <v>7</v>
       </c>
       <c r="C208" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D208">
         <v>91</v>
@@ -12179,7 +12340,7 @@
         <v>7</v>
       </c>
       <c r="C209" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D209">
         <v>77</v>
@@ -12196,7 +12357,7 @@
         <v>8</v>
       </c>
       <c r="C210" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D210">
         <v>72</v>
@@ -12213,7 +12374,7 @@
         <v>8</v>
       </c>
       <c r="C211" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D211">
         <v>59</v>
@@ -12230,7 +12391,7 @@
         <v>8</v>
       </c>
       <c r="C212" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D212">
         <v>33</v>
@@ -12247,7 +12408,7 @@
         <v>8</v>
       </c>
       <c r="C213" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D213">
         <v>88</v>
@@ -12264,7 +12425,7 @@
         <v>8</v>
       </c>
       <c r="C214" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D214">
         <v>107</v>
@@ -12281,7 +12442,7 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D215">
         <v>79</v>
@@ -12298,7 +12459,7 @@
         <v>9</v>
       </c>
       <c r="C216" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D216">
         <v>92</v>
@@ -12315,7 +12476,7 @@
         <v>9</v>
       </c>
       <c r="C217" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D217">
         <v>68</v>
@@ -12332,7 +12493,7 @@
         <v>9</v>
       </c>
       <c r="C218" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D218">
         <v>40</v>
@@ -12349,7 +12510,7 @@
         <v>9</v>
       </c>
       <c r="C219" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D219">
         <v>73</v>
@@ -12366,7 +12527,7 @@
         <v>9</v>
       </c>
       <c r="C220" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D220">
         <v>88</v>
@@ -12383,7 +12544,7 @@
         <v>9</v>
       </c>
       <c r="C221" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D221">
         <v>82</v>
@@ -12400,7 +12561,7 @@
         <v>10</v>
       </c>
       <c r="C222" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D222">
         <v>81</v>
@@ -12417,7 +12578,7 @@
         <v>10</v>
       </c>
       <c r="C223" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D223">
         <v>60</v>
@@ -12434,7 +12595,7 @@
         <v>10</v>
       </c>
       <c r="C224" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D224">
         <v>40</v>
@@ -12451,7 +12612,7 @@
         <v>10</v>
       </c>
       <c r="C225" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D225">
         <v>97</v>
@@ -12468,7 +12629,7 @@
         <v>10</v>
       </c>
       <c r="C226" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D226">
         <v>106</v>
@@ -12485,7 +12646,7 @@
         <v>10</v>
       </c>
       <c r="C227" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D227">
         <v>93</v>
@@ -12502,7 +12663,7 @@
         <v>11</v>
       </c>
       <c r="C228" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D228">
         <v>80</v>
@@ -12519,7 +12680,7 @@
         <v>11</v>
       </c>
       <c r="C229" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D229">
         <v>78</v>
@@ -12536,7 +12697,7 @@
         <v>11</v>
       </c>
       <c r="C230" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D230">
         <v>25</v>
@@ -12553,7 +12714,7 @@
         <v>11</v>
       </c>
       <c r="C231" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D231">
         <v>94</v>
@@ -12570,7 +12731,7 @@
         <v>11</v>
       </c>
       <c r="C232" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D232">
         <v>112</v>
@@ -12587,7 +12748,7 @@
         <v>11</v>
       </c>
       <c r="C233" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D233">
         <v>87</v>
@@ -12604,7 +12765,7 @@
         <v>12</v>
       </c>
       <c r="C234" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D234">
         <v>94</v>
@@ -12621,7 +12782,7 @@
         <v>12</v>
       </c>
       <c r="C235" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D235">
         <v>74</v>
@@ -12638,7 +12799,7 @@
         <v>12</v>
       </c>
       <c r="C236" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D236">
         <v>34</v>
@@ -12655,7 +12816,7 @@
         <v>12</v>
       </c>
       <c r="C237" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D237">
         <v>87</v>
@@ -12672,7 +12833,7 @@
         <v>12</v>
       </c>
       <c r="C238" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D238">
         <v>122</v>
@@ -12689,7 +12850,7 @@
         <v>12</v>
       </c>
       <c r="C239" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D239">
         <v>51</v>
@@ -12706,7 +12867,7 @@
         <v>1</v>
       </c>
       <c r="C240" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D240">
         <v>160</v>
@@ -12723,7 +12884,7 @@
         <v>1</v>
       </c>
       <c r="C241" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D241">
         <v>127</v>
@@ -12740,7 +12901,7 @@
         <v>1</v>
       </c>
       <c r="C242" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D242">
         <v>70</v>
@@ -12757,7 +12918,7 @@
         <v>1</v>
       </c>
       <c r="C243" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D243">
         <v>197</v>
@@ -12774,7 +12935,7 @@
         <v>1</v>
       </c>
       <c r="C244" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D244">
         <v>147</v>
@@ -12791,7 +12952,7 @@
         <v>1</v>
       </c>
       <c r="C245" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D245">
         <v>50</v>
@@ -12808,7 +12969,7 @@
         <v>2</v>
       </c>
       <c r="C246" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D246">
         <v>147</v>
@@ -12825,7 +12986,7 @@
         <v>2</v>
       </c>
       <c r="C247" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D247">
         <v>100</v>
@@ -12842,7 +13003,7 @@
         <v>2</v>
       </c>
       <c r="C248" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D248">
         <v>49</v>
@@ -12859,7 +13020,7 @@
         <v>2</v>
       </c>
       <c r="C249" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D249">
         <v>183</v>
@@ -12876,7 +13037,7 @@
         <v>2</v>
       </c>
       <c r="C250" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D250">
         <v>149</v>
@@ -12893,7 +13054,7 @@
         <v>2</v>
       </c>
       <c r="C251" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D251">
         <v>44</v>
@@ -12910,7 +13071,7 @@
         <v>3</v>
       </c>
       <c r="C252" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D252">
         <v>126</v>
@@ -12927,7 +13088,7 @@
         <v>3</v>
       </c>
       <c r="C253" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D253">
         <v>121</v>
@@ -12944,7 +13105,7 @@
         <v>3</v>
       </c>
       <c r="C254" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D254">
         <v>59</v>
@@ -12961,7 +13122,7 @@
         <v>3</v>
       </c>
       <c r="C255" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D255">
         <v>166</v>
@@ -12978,7 +13139,7 @@
         <v>3</v>
       </c>
       <c r="C256" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D256">
         <v>179</v>
@@ -12995,7 +13156,7 @@
         <v>3</v>
       </c>
       <c r="C257" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D257">
         <v>65</v>
@@ -13012,7 +13173,7 @@
         <v>4</v>
       </c>
       <c r="C258" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D258">
         <v>194</v>
@@ -13029,7 +13190,7 @@
         <v>4</v>
       </c>
       <c r="C259" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D259">
         <v>169</v>
@@ -13046,7 +13207,7 @@
         <v>4</v>
       </c>
       <c r="C260" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D260">
         <v>82</v>
@@ -13063,7 +13224,7 @@
         <v>4</v>
       </c>
       <c r="C261" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D261">
         <v>226</v>
@@ -13080,7 +13241,7 @@
         <v>4</v>
       </c>
       <c r="C262" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D262">
         <v>102</v>
@@ -13097,7 +13258,7 @@
         <v>4</v>
       </c>
       <c r="C263" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D263">
         <v>98</v>
@@ -13114,7 +13275,7 @@
         <v>5</v>
       </c>
       <c r="C264" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D264">
         <v>213</v>
@@ -13131,7 +13292,7 @@
         <v>5</v>
       </c>
       <c r="C265" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D265">
         <v>175</v>
@@ -13148,7 +13309,7 @@
         <v>5</v>
       </c>
       <c r="C266" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D266">
         <v>97</v>
@@ -13165,7 +13326,7 @@
         <v>5</v>
       </c>
       <c r="C267" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D267">
         <v>267</v>
@@ -13182,7 +13343,7 @@
         <v>5</v>
       </c>
       <c r="C268" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D268">
         <v>110</v>
@@ -13199,7 +13360,7 @@
         <v>5</v>
       </c>
       <c r="C269" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D269">
         <v>103</v>
@@ -13216,7 +13377,7 @@
         <v>6</v>
       </c>
       <c r="C270" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D270">
         <v>197</v>
@@ -13233,7 +13394,7 @@
         <v>6</v>
       </c>
       <c r="C271" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D271">
         <v>140</v>
@@ -13250,7 +13411,7 @@
         <v>6</v>
       </c>
       <c r="C272" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D272">
         <v>94</v>
@@ -13267,7 +13428,7 @@
         <v>6</v>
       </c>
       <c r="C273" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D273">
         <v>256</v>
@@ -13284,7 +13445,7 @@
         <v>6</v>
       </c>
       <c r="C274" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D274">
         <v>108</v>
@@ -13301,7 +13462,7 @@
         <v>6</v>
       </c>
       <c r="C275" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D275">
         <v>119</v>
@@ -13318,7 +13479,7 @@
         <v>7</v>
       </c>
       <c r="C276" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D276">
         <v>123</v>
@@ -13335,7 +13496,7 @@
         <v>7</v>
       </c>
       <c r="C277" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D277">
         <v>113</v>
@@ -13352,7 +13513,7 @@
         <v>7</v>
       </c>
       <c r="C278" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D278">
         <v>58</v>
@@ -13369,7 +13530,7 @@
         <v>7</v>
       </c>
       <c r="C279" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D279">
         <v>141</v>
@@ -13386,7 +13547,7 @@
         <v>7</v>
       </c>
       <c r="C280" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D280">
         <v>137</v>
@@ -13403,7 +13564,7 @@
         <v>7</v>
       </c>
       <c r="C281" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D281">
         <v>76</v>
@@ -13420,7 +13581,7 @@
         <v>8</v>
       </c>
       <c r="C282" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D282">
         <v>111</v>
@@ -13437,7 +13598,7 @@
         <v>8</v>
       </c>
       <c r="C283" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D283">
         <v>95</v>
@@ -13454,7 +13615,7 @@
         <v>8</v>
       </c>
       <c r="C284" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D284">
         <v>64</v>
@@ -13471,7 +13632,7 @@
         <v>8</v>
       </c>
       <c r="C285" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D285">
         <v>167</v>
@@ -13488,7 +13649,7 @@
         <v>8</v>
       </c>
       <c r="C286" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D286">
         <v>154</v>
@@ -13505,7 +13666,7 @@
         <v>8</v>
       </c>
       <c r="C287" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D287">
         <v>78</v>
@@ -13522,7 +13683,7 @@
         <v>9</v>
       </c>
       <c r="C288" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D288">
         <v>143</v>
@@ -13539,7 +13700,7 @@
         <v>9</v>
       </c>
       <c r="C289" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D289">
         <v>121</v>
@@ -13556,7 +13717,7 @@
         <v>9</v>
       </c>
       <c r="C290" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D290">
         <v>59</v>
@@ -13573,7 +13734,7 @@
         <v>9</v>
       </c>
       <c r="C291" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D291">
         <v>157</v>
@@ -13590,7 +13751,7 @@
         <v>9</v>
       </c>
       <c r="C292" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D292">
         <v>161</v>
@@ -13607,7 +13768,7 @@
         <v>9</v>
       </c>
       <c r="C293" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D293">
         <v>74</v>
@@ -13624,7 +13785,7 @@
         <v>10</v>
       </c>
       <c r="C294" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D294">
         <v>200</v>
@@ -13641,7 +13802,7 @@
         <v>10</v>
       </c>
       <c r="C295" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D295">
         <v>172</v>
@@ -13658,7 +13819,7 @@
         <v>10</v>
       </c>
       <c r="C296" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D296">
         <v>92</v>
@@ -13675,7 +13836,7 @@
         <v>10</v>
       </c>
       <c r="C297" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D297">
         <v>238</v>
@@ -13692,7 +13853,7 @@
         <v>10</v>
       </c>
       <c r="C298" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D298">
         <v>271</v>
@@ -13709,7 +13870,7 @@
         <v>10</v>
       </c>
       <c r="C299" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D299">
         <v>115</v>
@@ -13726,7 +13887,7 @@
         <v>11</v>
       </c>
       <c r="C300" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D300">
         <v>122</v>
@@ -13743,7 +13904,7 @@
         <v>11</v>
       </c>
       <c r="C301" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D301">
         <v>122</v>
@@ -13760,7 +13921,7 @@
         <v>11</v>
       </c>
       <c r="C302" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D302">
         <v>58</v>
@@ -13777,7 +13938,7 @@
         <v>11</v>
       </c>
       <c r="C303" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D303">
         <v>168</v>
@@ -13794,7 +13955,7 @@
         <v>11</v>
       </c>
       <c r="C304" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D304">
         <v>172</v>
@@ -13811,7 +13972,7 @@
         <v>11</v>
       </c>
       <c r="C305" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D305">
         <v>72</v>
@@ -13828,7 +13989,7 @@
         <v>12</v>
       </c>
       <c r="C306" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D306">
         <v>169</v>
@@ -13845,7 +14006,7 @@
         <v>12</v>
       </c>
       <c r="C307" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D307">
         <v>107</v>
@@ -13862,7 +14023,7 @@
         <v>12</v>
       </c>
       <c r="C308" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D308">
         <v>70</v>
@@ -13879,7 +14040,7 @@
         <v>12</v>
       </c>
       <c r="C309" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D309">
         <v>170</v>
@@ -13896,7 +14057,7 @@
         <v>12</v>
       </c>
       <c r="C310" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D310">
         <v>169</v>
@@ -13913,7 +14074,7 @@
         <v>12</v>
       </c>
       <c r="C311" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D311">
         <v>73</v>
@@ -13934,7 +14095,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D34F8D5-B786-45B8-BFC3-6C1BBDFF9C48}">
-  <dimension ref="A7:B54"/>
+  <dimension ref="A7:B57"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
@@ -13944,15 +14105,15 @@
   <sheetData>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
         <v>26</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" s="4">
         <v>0.70057470007317668</v>
@@ -13960,7 +14121,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" s="4">
         <v>0.29942529992682343</v>
@@ -13968,177 +14129,177 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" s="4">
         <v>1</v>
       </c>
     </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
+        <v>19</v>
+      </c>
+    </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" t="s">
-        <v>20</v>
+      <c r="A25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="4">
+        <v>1.5929326869437436E-2</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B26" s="4">
-        <v>1.5929326869437436E-2</v>
+        <v>7.8805283793012326E-2</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B27" s="4">
-        <v>7.8805283793012326E-2</v>
+        <v>8.213184872907868E-2</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B28" s="4">
-        <v>8.213184872907868E-2</v>
+        <v>8.5183667846208386E-2</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B29" s="4">
-        <v>8.5183667846208386E-2</v>
+        <v>8.5722746505192599E-2</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B30" s="4">
-        <v>8.5722746505192599E-2</v>
+        <v>8.7221922883620059E-2</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B31" s="4">
-        <v>8.7221922883620059E-2</v>
+        <v>8.7237052277785582E-2</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B32" s="4">
-        <v>8.7237052277785582E-2</v>
+        <v>9.1469277202132118E-2</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B33" s="4">
-        <v>9.1469277202132118E-2</v>
+        <v>9.6762619492480315E-2</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B34" s="4">
-        <v>9.6762619492480315E-2</v>
+        <v>0.10292218469821034</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B35" s="4">
-        <v>0.10292218469821034</v>
+        <v>0.18661406970284225</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B36" s="4">
-        <v>0.18661406970284225</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B47" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B48">
-        <v>465.94915349999997</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B49">
-        <v>174.62502535416672</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B50">
-        <v>32.343998083333339</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B51">
-        <v>31.639881937500007</v>
+        <v>465.94915349999997</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B52">
-        <v>29.195210708333331</v>
+        <v>174.62502535416672</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B53">
-        <v>10.105105000000002</v>
+        <v>32.343998083333339</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="B54">
+        <v>31.639881937500007</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B55">
+        <v>29.195210708333331</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B56">
+        <v>10.105105000000002</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57">
         <v>123.9763957638889</v>
       </c>
     </row>
@@ -14716,10 +14877,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -15140,7 +15301,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B54">
         <v>3417850.0100000002</v>

--- a/Chanthadara_territory_chart.xlsx
+++ b/Chanthadara_territory_chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chimm\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C7B0D09-7659-4CD1-8EA3-3FBDCC20A2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D502FD57-02E1-4F91-A503-129DF24FDC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4F9622DB-3F0B-4399-96EC-3CBDB6BB25F8}"/>
   </bookViews>
@@ -8047,6 +8047,98 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6B0FE92-A8F0-44F2-81AE-8F660C0D359C}" name="PivotTable7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Categories">
+  <location ref="A50:B57" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average Transactions" fld="4" subtotal="average" baseField="2" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CD5EED47-6634-433F-8246-8166C77A8301}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6" rowHeaderCaption="Territory">
   <location ref="A7:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
@@ -8126,7 +8218,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4F5F414B-C686-4F7F-BA97-F099CE7B7DB1}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18" rowHeaderCaption="Store Location">
   <location ref="A24:B36" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
@@ -8234,98 +8326,6 @@
   </colItems>
   <dataFields count="1">
     <dataField name="% of Revenue for Texas" fld="2" showDataAs="percentOfTotal" baseField="1" baseItem="4" numFmtId="10"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6B0FE92-A8F0-44F2-81AE-8F660C0D359C}" name="PivotTable7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Categories">
-  <location ref="A50:B57" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average Transactions" fld="4" subtotal="average" baseField="2" baseItem="0"/>
   </dataFields>
   <chartFormats count="1">
     <chartFormat chart="0" format="0" series="1">

--- a/Chanthadara_territory_chart.xlsx
+++ b/Chanthadara_territory_chart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chimm\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D502FD57-02E1-4F91-A503-129DF24FDC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEDA2E0A-1B2D-4AEC-A129-44F09A8AC823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4F9622DB-3F0B-4399-96EC-3CBDB6BB25F8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4F9622DB-3F0B-4399-96EC-3CBDB6BB25F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Findings" sheetId="7" r:id="rId1"/>
@@ -8047,178 +8047,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6B0FE92-A8F0-44F2-81AE-8F660C0D359C}" name="PivotTable7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Categories">
-  <location ref="A50:B57" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average Transactions" fld="4" subtotal="average" baseField="2" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CD5EED47-6634-433F-8246-8166C77A8301}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6" rowHeaderCaption="Territory">
-  <location ref="A7:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="% of Total_Revenue" fld="1" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="10"/>
-  </dataFields>
-  <chartFormats count="3">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4F5F414B-C686-4F7F-BA97-F099CE7B7DB1}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18" rowHeaderCaption="Store Location">
   <location ref="A24:B36" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
@@ -8333,6 +8161,178 @@
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6B0FE92-A8F0-44F2-81AE-8F660C0D359C}" name="PivotTable7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Categories">
+  <location ref="A50:B57" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average Transactions" fld="4" subtotal="average" baseField="2" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CD5EED47-6634-433F-8246-8166C77A8301}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6" rowHeaderCaption="Territory">
+  <location ref="A7:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="% of Total_Revenue" fld="1" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>

--- a/Chanthadara_territory_chart.xlsx
+++ b/Chanthadara_territory_chart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chimm\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEDA2E0A-1B2D-4AEC-A129-44F09A8AC823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{16DC384D-B764-4646-A005-A43770CCC189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4F9622DB-3F0B-4399-96EC-3CBDB6BB25F8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4F9622DB-3F0B-4399-96EC-3CBDB6BB25F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Findings" sheetId="7" r:id="rId1"/>

--- a/Chanthadara_territory_chart.xlsx
+++ b/Chanthadara_territory_chart.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chimm\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16DC384D-B764-4646-A005-A43770CCC189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CADDF0E1-C1DE-49A8-9FB1-F25C5FF5DC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4F9622DB-3F0B-4399-96EC-3CBDB6BB25F8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="1" xr2:uid="{4F9622DB-3F0B-4399-96EC-3CBDB6BB25F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Findings" sheetId="7" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <definedName name="ExternalData_3" localSheetId="0" hidden="1">Findings!$A$2:$B$4</definedName>
     <definedName name="ExternalData_4" localSheetId="0" hidden="1">Findings!$A$23:$E$311</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId5"/>
     <pivotCache cacheId="1" r:id="rId6"/>
@@ -79,19 +79,22 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="40">
   <si>
-    <t>Year</t>
+    <t>Texas VS South Region</t>
   </si>
   <si>
-    <t>Month</t>
+    <t>Location</t>
   </si>
   <si>
     <t>Total_Revenue</t>
   </si>
   <si>
-    <t>Grand Total</t>
+    <t>Texas</t>
   </si>
   <si>
-    <t>Sum of Total_Revenue</t>
+    <t>South</t>
+  </si>
+  <si>
+    <t>Performance Table</t>
   </si>
   <si>
     <t>StoreId</t>
@@ -133,31 +136,13 @@
     <t>Dallas</t>
   </si>
   <si>
-    <t>Store Location</t>
+    <t>TexasAvgSale</t>
   </si>
   <si>
-    <t>% of Revenue for Texas</t>
+    <t>Year</t>
   </si>
   <si>
-    <t>Performance Table</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Texas</t>
-  </si>
-  <si>
-    <t>South</t>
-  </si>
-  <si>
-    <t>Texas VS South Region</t>
-  </si>
-  <si>
-    <t>Territory</t>
-  </si>
-  <si>
-    <t>% of Total_Revenue</t>
+    <t>Month</t>
   </si>
   <si>
     <t>Category</t>
@@ -187,7 +172,19 @@
     <t>Textbooks</t>
   </si>
   <si>
-    <t>TexasAvgSale</t>
+    <t>Territory</t>
+  </si>
+  <si>
+    <t>% of Total_Revenue</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Store Location</t>
+  </si>
+  <si>
+    <t>% of Revenue for Texas</t>
   </si>
   <si>
     <t>Categories</t>
@@ -196,7 +193,10 @@
     <t>Average Transactions</t>
   </si>
   <si>
-    <t>Year&amp;Months</t>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Sum of Total_Revenue</t>
   </si>
 </sst>
 </file>
@@ -434,7 +434,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Findings_Chart!$B$24</c:f>
+              <c:f>Findings_Chart!$B$25</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -532,7 +532,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Findings_Chart!$A$25:$A$36</c:f>
+              <c:f>Findings_Chart!$A$26:$A$37</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -573,7 +573,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Findings_Chart!$B$25:$B$36</c:f>
+              <c:f>Findings_Chart!$B$26:$B$37</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="11"/>
@@ -1821,31 +1821,6 @@
   </c:pivotSource>
   <c:chart>
     <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Transactions</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1945,7 +1920,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Findings_Chart!$B$50</c:f>
+              <c:f>Findings_Chart!$B$47</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1966,7 +1941,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Findings_Chart!$A$51:$A$57</c:f>
+              <c:f>Findings_Chart!$A$48:$A$54</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -1992,7 +1967,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Findings_Chart!$B$51:$B$57</c:f>
+              <c:f>Findings_Chart!$B$48:$B$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2198,13 +2173,8 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Average</a:t>
+                  <a:t>Average Transactions</a:t>
                 </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t> Transactions</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -5390,9 +5360,9 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>518160</xdr:colOff>
+      <xdr:colOff>594360</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:rowOff>175260</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
@@ -5467,10 +5437,10 @@
       <xdr:rowOff>3810</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>167640</xdr:rowOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5478,6 +5448,9 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E7C2DD9-695B-299C-D522-0E3DD4BE7762}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{DDD027AA-D0EE-0F6B-437D-B9783A8ADA33}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5502,16 +5475,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>601980</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5666,18 +5639,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Alexus Chanthadara " refreshedDate="46141.512932291669" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="288" xr:uid="{6C9FF4FB-CB9C-40C7-94C3-03014FB7F063}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Excel Services" refreshedDate="46141.787238888886" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="288" xr:uid="{6C9FF4FB-CB9C-40C7-94C3-03014FB7F063}">
   <cacheSource type="worksheet">
     <worksheetSource name="capstone_TexasAvgSale9"/>
   </cacheSource>
   <cacheFields count="5">
     <cacheField name="Year" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2022" maxValue="2025" count="4">
-        <n v="2022"/>
-        <n v="2023"/>
-        <n v="2024"/>
-        <n v="2025"/>
-      </sharedItems>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2022" maxValue="2025"/>
     </cacheField>
     <cacheField name="Month" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="12"/>
@@ -6028,2016 +5996,2016 @@
 <file path=xl/pivotCache/pivotCacheRecords4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="288">
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="1"/>
     <x v="0"/>
     <n v="55"/>
     <n v="32.792000000000002"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="1"/>
     <x v="1"/>
     <n v="44"/>
     <n v="31.695682000000001"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="1"/>
     <x v="2"/>
     <n v="28"/>
     <n v="27.960356999999998"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="1"/>
     <x v="3"/>
     <n v="69"/>
     <n v="10.546232"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="1"/>
     <x v="4"/>
     <n v="69"/>
     <n v="369.81826100000001"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="1"/>
     <x v="5"/>
     <n v="56"/>
     <n v="189.83910700000001"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="2"/>
     <x v="0"/>
     <n v="66"/>
     <n v="32.163485000000001"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="2"/>
     <x v="1"/>
     <n v="49"/>
     <n v="25.011019999999998"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="2"/>
     <x v="2"/>
     <n v="23"/>
     <n v="30.761303999999999"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="2"/>
     <x v="3"/>
     <n v="50"/>
     <n v="11.0528"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="2"/>
     <x v="4"/>
     <n v="80"/>
     <n v="476.089"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="2"/>
     <x v="5"/>
     <n v="56"/>
     <n v="179.171786"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="3"/>
     <x v="0"/>
     <n v="50"/>
     <n v="31.235600000000002"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="3"/>
     <x v="1"/>
     <n v="42"/>
     <n v="34.806190000000001"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="3"/>
     <x v="2"/>
     <n v="29"/>
     <n v="28.877586000000001"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="3"/>
     <x v="3"/>
     <n v="63"/>
     <n v="10.746667"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="3"/>
     <x v="4"/>
     <n v="63"/>
     <n v="533.86952399999996"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="3"/>
     <x v="5"/>
     <n v="60"/>
     <n v="184.050667"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="4"/>
     <x v="0"/>
     <n v="35"/>
     <n v="32.735714000000002"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="4"/>
     <x v="1"/>
     <n v="51"/>
     <n v="33.566077999999997"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="4"/>
     <x v="2"/>
     <n v="31"/>
     <n v="27.52129"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="4"/>
     <x v="3"/>
     <n v="64"/>
     <n v="10.724531000000001"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="4"/>
     <x v="4"/>
     <n v="82"/>
     <n v="490.10365899999999"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="4"/>
     <x v="5"/>
     <n v="58"/>
     <n v="183.510345"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="5"/>
     <x v="0"/>
     <n v="55"/>
     <n v="33.479635999999999"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="5"/>
     <x v="1"/>
     <n v="47"/>
     <n v="33.459361999999999"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="5"/>
     <x v="2"/>
     <n v="26"/>
     <n v="31.585384999999999"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="5"/>
     <x v="3"/>
     <n v="55"/>
     <n v="9.5609090000000005"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="5"/>
     <x v="4"/>
     <n v="79"/>
     <n v="385.08721500000001"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="5"/>
     <x v="5"/>
     <n v="76"/>
     <n v="190.97434200000001"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="6"/>
     <x v="0"/>
     <n v="62"/>
     <n v="33.568387000000001"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="6"/>
     <x v="1"/>
     <n v="55"/>
     <n v="31.306182"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="6"/>
     <x v="2"/>
     <n v="26"/>
     <n v="24.891538000000001"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="6"/>
     <x v="3"/>
     <n v="76"/>
     <n v="9.8276319999999995"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="6"/>
     <x v="4"/>
     <n v="57"/>
     <n v="548.59508800000003"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="6"/>
     <x v="5"/>
     <n v="47"/>
     <n v="185.982553"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="7"/>
     <x v="0"/>
     <n v="48"/>
     <n v="31.456042"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="7"/>
     <x v="1"/>
     <n v="49"/>
     <n v="34.168979999999998"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="7"/>
     <x v="2"/>
     <n v="26"/>
     <n v="25.784614999999999"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="7"/>
     <x v="3"/>
     <n v="77"/>
     <n v="10.325195000000001"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="7"/>
     <x v="4"/>
     <n v="66"/>
     <n v="460.07893899999999"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="7"/>
     <x v="5"/>
     <n v="73"/>
     <n v="182.10739699999999"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="8"/>
     <x v="0"/>
     <n v="57"/>
     <n v="29.886316000000001"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="8"/>
     <x v="1"/>
     <n v="39"/>
     <n v="32.516666999999998"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="8"/>
     <x v="2"/>
     <n v="23"/>
     <n v="26.856521999999998"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="8"/>
     <x v="3"/>
     <n v="69"/>
     <n v="10.905652"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="8"/>
     <x v="4"/>
     <n v="74"/>
     <n v="460.82783799999999"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="8"/>
     <x v="5"/>
     <n v="60"/>
     <n v="186.636833"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="9"/>
     <x v="0"/>
     <n v="59"/>
     <n v="34.588304999999998"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="9"/>
     <x v="1"/>
     <n v="52"/>
     <n v="33.091923000000001"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="9"/>
     <x v="2"/>
     <n v="28"/>
     <n v="31.76"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="9"/>
     <x v="3"/>
     <n v="70"/>
     <n v="9.6457139999999999"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="9"/>
     <x v="4"/>
     <n v="65"/>
     <n v="485.40353800000003"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="9"/>
     <x v="5"/>
     <n v="60"/>
     <n v="184.997333"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="10"/>
     <x v="0"/>
     <n v="56"/>
     <n v="30.823392999999999"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="10"/>
     <x v="1"/>
     <n v="56"/>
     <n v="29.619464000000001"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="10"/>
     <x v="2"/>
     <n v="21"/>
     <n v="33.872857000000003"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="10"/>
     <x v="3"/>
     <n v="75"/>
     <n v="9.5713329999999992"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="10"/>
     <x v="4"/>
     <n v="80"/>
     <n v="422.91087499999998"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="10"/>
     <x v="5"/>
     <n v="69"/>
     <n v="172.40942000000001"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="11"/>
     <x v="0"/>
     <n v="54"/>
     <n v="30.550370000000001"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="11"/>
     <x v="1"/>
     <n v="41"/>
     <n v="30.232683000000002"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="11"/>
     <x v="2"/>
     <n v="30"/>
     <n v="28.027332999999999"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="11"/>
     <x v="3"/>
     <n v="71"/>
     <n v="11.168028"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="11"/>
     <x v="4"/>
     <n v="69"/>
     <n v="383.61333300000001"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="11"/>
     <x v="5"/>
     <n v="57"/>
     <n v="182.63421099999999"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="12"/>
     <x v="0"/>
     <n v="53"/>
     <n v="31.06"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="12"/>
     <x v="1"/>
     <n v="50"/>
     <n v="31.362200000000001"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="12"/>
     <x v="2"/>
     <n v="27"/>
     <n v="26.511481"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="12"/>
     <x v="3"/>
     <n v="61"/>
     <n v="9.531148"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="12"/>
     <x v="4"/>
     <n v="64"/>
     <n v="524.69796899999994"/>
   </r>
   <r>
-    <x v="0"/>
+    <n v="2022"/>
     <n v="12"/>
     <x v="5"/>
     <n v="60"/>
     <n v="182.727833"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="1"/>
     <x v="0"/>
     <n v="94"/>
     <n v="34.116596000000001"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="1"/>
     <x v="1"/>
     <n v="74"/>
     <n v="27.785135"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="1"/>
     <x v="2"/>
     <n v="34"/>
     <n v="36.060588000000003"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="1"/>
     <x v="3"/>
     <n v="87"/>
     <n v="10.301724"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="1"/>
     <x v="4"/>
     <n v="122"/>
     <n v="468.64123000000001"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="1"/>
     <x v="5"/>
     <n v="51"/>
     <n v="151.74568600000001"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="2"/>
     <x v="0"/>
     <n v="67"/>
     <n v="31.493880999999998"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="2"/>
     <x v="1"/>
     <n v="78"/>
     <n v="28.760897"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="2"/>
     <x v="2"/>
     <n v="20"/>
     <n v="27.143999999999998"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="2"/>
     <x v="3"/>
     <n v="89"/>
     <n v="9.8593259999999994"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="2"/>
     <x v="4"/>
     <n v="77"/>
     <n v="380.57220799999999"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="2"/>
     <x v="5"/>
     <n v="57"/>
     <n v="181.07912300000001"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="3"/>
     <x v="0"/>
     <n v="80"/>
     <n v="33.780999999999999"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="3"/>
     <x v="1"/>
     <n v="52"/>
     <n v="32.593845999999999"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="3"/>
     <x v="2"/>
     <n v="35"/>
     <n v="29.645143000000001"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="3"/>
     <x v="3"/>
     <n v="90"/>
     <n v="9.9535560000000007"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="3"/>
     <x v="4"/>
     <n v="112"/>
     <n v="457.593929"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="3"/>
     <x v="5"/>
     <n v="60"/>
     <n v="164.79133300000001"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="4"/>
     <x v="0"/>
     <n v="72"/>
     <n v="32.218333000000001"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="4"/>
     <x v="1"/>
     <n v="71"/>
     <n v="29.900986"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="4"/>
     <x v="2"/>
     <n v="32"/>
     <n v="22.66"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="4"/>
     <x v="3"/>
     <n v="127"/>
     <n v="9.7941730000000007"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="4"/>
     <x v="4"/>
     <n v="128"/>
     <n v="464.52249999999998"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="4"/>
     <x v="5"/>
     <n v="63"/>
     <n v="172.091905"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="5"/>
     <x v="0"/>
     <n v="72"/>
     <n v="31.782917000000001"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="5"/>
     <x v="1"/>
     <n v="65"/>
     <n v="31.317077000000001"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="5"/>
     <x v="2"/>
     <n v="36"/>
     <n v="30.120277999999999"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="5"/>
     <x v="3"/>
     <n v="93"/>
     <n v="9.0105380000000004"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="5"/>
     <x v="4"/>
     <n v="107"/>
     <n v="517.38766399999997"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="5"/>
     <x v="5"/>
     <n v="70"/>
     <n v="177.89585700000001"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="6"/>
     <x v="0"/>
     <n v="56"/>
     <n v="36.775536000000002"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="6"/>
     <x v="1"/>
     <n v="79"/>
     <n v="30.700506000000001"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="6"/>
     <x v="2"/>
     <n v="38"/>
     <n v="32.765526000000001"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="6"/>
     <x v="3"/>
     <n v="97"/>
     <n v="10.023918"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="6"/>
     <x v="4"/>
     <n v="107"/>
     <n v="460.71233599999999"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="6"/>
     <x v="5"/>
     <n v="66"/>
     <n v="186.99454499999999"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="7"/>
     <x v="0"/>
     <n v="88"/>
     <n v="30.687840999999999"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="7"/>
     <x v="1"/>
     <n v="60"/>
     <n v="31.5535"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="7"/>
     <x v="2"/>
     <n v="37"/>
     <n v="30.431080999999999"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="7"/>
     <x v="3"/>
     <n v="92"/>
     <n v="9.3784779999999994"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="7"/>
     <x v="4"/>
     <n v="98"/>
     <n v="456.56530600000002"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="7"/>
     <x v="5"/>
     <n v="76"/>
     <n v="165.988947"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="8"/>
     <x v="0"/>
     <n v="70"/>
     <n v="29.631857"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="8"/>
     <x v="1"/>
     <n v="80"/>
     <n v="30.547750000000001"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="8"/>
     <x v="2"/>
     <n v="35"/>
     <n v="29.713429000000001"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="8"/>
     <x v="3"/>
     <n v="102"/>
     <n v="11.479706"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="8"/>
     <x v="4"/>
     <n v="91"/>
     <n v="452.13692300000002"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="8"/>
     <x v="5"/>
     <n v="77"/>
     <n v="166.58649399999999"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="9"/>
     <x v="0"/>
     <n v="70"/>
     <n v="34.036000000000001"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="9"/>
     <x v="1"/>
     <n v="58"/>
     <n v="31.191033999999998"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="9"/>
     <x v="2"/>
     <n v="29"/>
     <n v="25.793102999999999"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="9"/>
     <x v="3"/>
     <n v="87"/>
     <n v="10.773562999999999"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="9"/>
     <x v="4"/>
     <n v="104"/>
     <n v="492.38817299999999"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="9"/>
     <x v="5"/>
     <n v="75"/>
     <n v="167.85146700000001"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="10"/>
     <x v="0"/>
     <n v="94"/>
     <n v="30.842127999999999"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="10"/>
     <x v="1"/>
     <n v="69"/>
     <n v="31.378405999999998"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="10"/>
     <x v="2"/>
     <n v="44"/>
     <n v="25.627955"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="10"/>
     <x v="3"/>
     <n v="74"/>
     <n v="10.003919"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="10"/>
     <x v="4"/>
     <n v="91"/>
     <n v="473.00054899999998"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="10"/>
     <x v="5"/>
     <n v="86"/>
     <n v="171.50976700000001"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="11"/>
     <x v="0"/>
     <n v="78"/>
     <n v="30.326667"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="11"/>
     <x v="1"/>
     <n v="59"/>
     <n v="30.405085"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="11"/>
     <x v="2"/>
     <n v="40"/>
     <n v="32.639499999999998"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="11"/>
     <x v="3"/>
     <n v="89"/>
     <n v="10.011011"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="11"/>
     <x v="4"/>
     <n v="103"/>
     <n v="426.68262099999998"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="11"/>
     <x v="5"/>
     <n v="89"/>
     <n v="171.33494400000001"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="12"/>
     <x v="0"/>
     <n v="83"/>
     <n v="32.684818999999997"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="12"/>
     <x v="1"/>
     <n v="79"/>
     <n v="31.994304"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="12"/>
     <x v="2"/>
     <n v="25"/>
     <n v="26.818000000000001"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="12"/>
     <x v="3"/>
     <n v="102"/>
     <n v="10.215686"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="12"/>
     <x v="4"/>
     <n v="115"/>
     <n v="481.44808699999999"/>
   </r>
   <r>
-    <x v="1"/>
+    <n v="2023"/>
     <n v="12"/>
     <x v="5"/>
     <n v="91"/>
     <n v="183.24054899999999"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="1"/>
     <x v="0"/>
     <n v="73"/>
     <n v="32.396163999999999"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="1"/>
     <x v="1"/>
     <n v="86"/>
     <n v="28.128256"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="1"/>
     <x v="2"/>
     <n v="23"/>
     <n v="26.910435"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="1"/>
     <x v="3"/>
     <n v="96"/>
     <n v="9.6534379999999995"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="1"/>
     <x v="4"/>
     <n v="88"/>
     <n v="363.20693199999999"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="1"/>
     <x v="5"/>
     <n v="63"/>
     <n v="183.05285699999999"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="2"/>
     <x v="0"/>
     <n v="77"/>
     <n v="33.68"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="2"/>
     <x v="1"/>
     <n v="46"/>
     <n v="33.996521999999999"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="2"/>
     <x v="2"/>
     <n v="33"/>
     <n v="30.024847999999999"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="2"/>
     <x v="3"/>
     <n v="85"/>
     <n v="10.212471000000001"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="2"/>
     <x v="4"/>
     <n v="103"/>
     <n v="480.27291300000002"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="2"/>
     <x v="5"/>
     <n v="56"/>
     <n v="161.8725"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="3"/>
     <x v="0"/>
     <n v="74"/>
     <n v="32.775945999999998"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="3"/>
     <x v="1"/>
     <n v="73"/>
     <n v="29.594932"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="3"/>
     <x v="2"/>
     <n v="33"/>
     <n v="22.849696999999999"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="3"/>
     <x v="3"/>
     <n v="128"/>
     <n v="9.788672"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="3"/>
     <x v="4"/>
     <n v="133"/>
     <n v="468.43691699999999"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="3"/>
     <x v="5"/>
     <n v="68"/>
     <n v="173.955735"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="4"/>
     <x v="0"/>
     <n v="70"/>
     <n v="31.181000000000001"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="4"/>
     <x v="1"/>
     <n v="63"/>
     <n v="31.716667000000001"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="4"/>
     <x v="2"/>
     <n v="35"/>
     <n v="30.154571000000001"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="4"/>
     <x v="3"/>
     <n v="92"/>
     <n v="9.0096740000000004"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="4"/>
     <x v="4"/>
     <n v="102"/>
     <n v="514.875"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="4"/>
     <x v="5"/>
     <n v="65"/>
     <n v="176.39246199999999"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="5"/>
     <x v="0"/>
     <n v="58"/>
     <n v="35.928966000000003"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="5"/>
     <x v="1"/>
     <n v="81"/>
     <n v="30.797284000000001"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="5"/>
     <x v="2"/>
     <n v="38"/>
     <n v="32.765526000000001"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="5"/>
     <x v="3"/>
     <n v="99"/>
     <n v="9.9476770000000005"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="5"/>
     <x v="4"/>
     <n v="111"/>
     <n v="458.59441399999997"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="5"/>
     <x v="5"/>
     <n v="70"/>
     <n v="186.01042899999999"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="6"/>
     <x v="0"/>
     <n v="86"/>
     <n v="31.117208999999999"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="6"/>
     <x v="1"/>
     <n v="58"/>
     <n v="31.447759000000001"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="6"/>
     <x v="2"/>
     <n v="37"/>
     <n v="30.431080999999999"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="6"/>
     <x v="3"/>
     <n v="90"/>
     <n v="9.4480000000000004"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="6"/>
     <x v="4"/>
     <n v="94"/>
     <n v="458.88978700000001"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="6"/>
     <x v="5"/>
     <n v="72"/>
     <n v="165.77875"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="7"/>
     <x v="0"/>
     <n v="70"/>
     <n v="29.631857"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="7"/>
     <x v="1"/>
     <n v="80"/>
     <n v="30.547750000000001"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="7"/>
     <x v="2"/>
     <n v="35"/>
     <n v="29.713429000000001"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="7"/>
     <x v="3"/>
     <n v="102"/>
     <n v="11.479706"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="7"/>
     <x v="4"/>
     <n v="91"/>
     <n v="452.13692300000002"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="7"/>
     <x v="5"/>
     <n v="77"/>
     <n v="166.58649399999999"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="8"/>
     <x v="0"/>
     <n v="72"/>
     <n v="34.027222000000002"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="8"/>
     <x v="1"/>
     <n v="59"/>
     <n v="30.943729000000001"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="8"/>
     <x v="2"/>
     <n v="33"/>
     <n v="25.542424"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="8"/>
     <x v="3"/>
     <n v="88"/>
     <n v="10.725227"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="8"/>
     <x v="4"/>
     <n v="107"/>
     <n v="487.18476600000002"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="8"/>
     <x v="5"/>
     <n v="79"/>
     <n v="168.64455699999999"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="9"/>
     <x v="0"/>
     <n v="92"/>
     <n v="30.779565000000002"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="9"/>
     <x v="1"/>
     <n v="68"/>
     <n v="31.595735000000001"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="9"/>
     <x v="2"/>
     <n v="40"/>
     <n v="25.818249999999999"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="9"/>
     <x v="3"/>
     <n v="73"/>
     <n v="10.051644"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="9"/>
     <x v="4"/>
     <n v="88"/>
     <n v="478.66647699999999"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="9"/>
     <x v="5"/>
     <n v="82"/>
     <n v="170.92414600000001"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="10"/>
     <x v="0"/>
     <n v="81"/>
     <n v="30.686173"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="10"/>
     <x v="1"/>
     <n v="60"/>
     <n v="30.96"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="10"/>
     <x v="2"/>
     <n v="40"/>
     <n v="32.639499999999998"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="10"/>
     <x v="3"/>
     <n v="97"/>
     <n v="10.001443"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="10"/>
     <x v="4"/>
     <n v="106"/>
     <n v="450.69896199999999"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="10"/>
     <x v="5"/>
     <n v="93"/>
     <n v="171.49419399999999"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="11"/>
     <x v="0"/>
     <n v="80"/>
     <n v="32.40925"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="11"/>
     <x v="1"/>
     <n v="78"/>
     <n v="31.587821000000002"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="11"/>
     <x v="2"/>
     <n v="25"/>
     <n v="26.818000000000001"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="11"/>
     <x v="3"/>
     <n v="94"/>
     <n v="10.242979"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="11"/>
     <x v="4"/>
     <n v="112"/>
     <n v="460.18526800000001"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="11"/>
     <x v="5"/>
     <n v="87"/>
     <n v="183.61770100000001"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="12"/>
     <x v="0"/>
     <n v="94"/>
     <n v="34.116596000000001"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="12"/>
     <x v="1"/>
     <n v="74"/>
     <n v="27.785135"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="12"/>
     <x v="2"/>
     <n v="34"/>
     <n v="36.060588000000003"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="12"/>
     <x v="3"/>
     <n v="87"/>
     <n v="10.301724"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="12"/>
     <x v="4"/>
     <n v="122"/>
     <n v="468.64123000000001"/>
   </r>
   <r>
-    <x v="2"/>
+    <n v="2024"/>
     <n v="12"/>
     <x v="5"/>
     <n v="51"/>
     <n v="151.74568600000001"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="1"/>
     <x v="0"/>
     <n v="160"/>
     <n v="33.761187999999997"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="1"/>
     <x v="1"/>
     <n v="127"/>
     <n v="34.387873999999996"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="1"/>
     <x v="2"/>
     <n v="70"/>
     <n v="26.949142999999999"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="1"/>
     <x v="3"/>
     <n v="197"/>
     <n v="9.8218779999999999"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="1"/>
     <x v="4"/>
     <n v="147"/>
     <n v="530.65986399999997"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="1"/>
     <x v="5"/>
     <n v="50"/>
     <n v="188.9744"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="2"/>
     <x v="0"/>
     <n v="147"/>
     <n v="31.623946"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="2"/>
     <x v="1"/>
     <n v="100"/>
     <n v="30.065899999999999"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="2"/>
     <x v="2"/>
     <n v="49"/>
     <n v="27.870612000000001"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="2"/>
     <x v="3"/>
     <n v="183"/>
     <n v="9.203989"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="2"/>
     <x v="4"/>
     <n v="149"/>
     <n v="516.58744999999999"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="2"/>
     <x v="5"/>
     <n v="44"/>
     <n v="166.596136"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="3"/>
     <x v="0"/>
     <n v="126"/>
     <n v="33.739840999999998"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="3"/>
     <x v="1"/>
     <n v="121"/>
     <n v="32.651404999999997"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="3"/>
     <x v="2"/>
     <n v="59"/>
     <n v="30.960339000000001"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="3"/>
     <x v="3"/>
     <n v="166"/>
     <n v="10.199699000000001"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="3"/>
     <x v="4"/>
     <n v="179"/>
     <n v="438.11486000000002"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="3"/>
     <x v="5"/>
     <n v="65"/>
     <n v="174.555846"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="4"/>
     <x v="0"/>
     <n v="194"/>
     <n v="31.796185999999999"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="4"/>
     <x v="1"/>
     <n v="169"/>
     <n v="35.852367000000001"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="4"/>
     <x v="2"/>
     <n v="82"/>
     <n v="29.770731999999999"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="4"/>
     <x v="3"/>
     <n v="226"/>
     <n v="9.9901769999999992"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="4"/>
     <x v="4"/>
     <n v="102"/>
     <n v="466.68754899999999"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="4"/>
     <x v="5"/>
     <n v="98"/>
     <n v="171.632755"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="5"/>
     <x v="0"/>
     <n v="213"/>
     <n v="31.911925"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="5"/>
     <x v="1"/>
     <n v="175"/>
     <n v="34.374229"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="5"/>
     <x v="2"/>
     <n v="97"/>
     <n v="33.582886999999999"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="5"/>
     <x v="3"/>
     <n v="267"/>
     <n v="10.282659000000001"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="5"/>
     <x v="4"/>
     <n v="110"/>
     <n v="443.83327300000002"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="5"/>
     <x v="5"/>
     <n v="103"/>
     <n v="176.34786399999999"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="6"/>
     <x v="0"/>
     <n v="197"/>
     <n v="30.710863"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="6"/>
     <x v="1"/>
     <n v="140"/>
     <n v="36.499357000000003"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="6"/>
     <x v="2"/>
     <n v="94"/>
     <n v="29.927021"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="6"/>
     <x v="3"/>
     <n v="256"/>
     <n v="9.9058200000000003"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="6"/>
     <x v="4"/>
     <n v="108"/>
     <n v="469.97537"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="6"/>
     <x v="5"/>
     <n v="119"/>
     <n v="167.365882"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="7"/>
     <x v="0"/>
     <n v="123"/>
     <n v="31.825854"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="7"/>
     <x v="1"/>
     <n v="113"/>
     <n v="34.748938000000003"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="7"/>
     <x v="2"/>
     <n v="58"/>
     <n v="29.634482999999999"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="7"/>
     <x v="3"/>
     <n v="141"/>
     <n v="10.030922"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="7"/>
     <x v="4"/>
     <n v="137"/>
     <n v="486.79635000000002"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="7"/>
     <x v="5"/>
     <n v="76"/>
     <n v="178.700132"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="8"/>
     <x v="0"/>
     <n v="111"/>
     <n v="29.707567999999998"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="8"/>
     <x v="1"/>
     <n v="95"/>
     <n v="32.433053000000001"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="8"/>
     <x v="2"/>
     <n v="64"/>
     <n v="26.588906000000001"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="8"/>
     <x v="3"/>
     <n v="167"/>
     <n v="9.8577250000000003"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="8"/>
     <x v="4"/>
     <n v="154"/>
     <n v="488.30220800000001"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="8"/>
     <x v="5"/>
     <n v="78"/>
     <n v="175.71512799999999"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="9"/>
     <x v="0"/>
     <n v="143"/>
     <n v="33.460839"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="9"/>
     <x v="1"/>
     <n v="121"/>
     <n v="32.266033"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="9"/>
     <x v="2"/>
     <n v="59"/>
     <n v="29.649660999999998"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="9"/>
     <x v="3"/>
     <n v="157"/>
     <n v="10.209427"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="9"/>
     <x v="4"/>
     <n v="161"/>
     <n v="528.47049700000002"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="9"/>
     <x v="5"/>
     <n v="74"/>
     <n v="161.36337800000001"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="10"/>
     <x v="0"/>
     <n v="200"/>
     <n v="31.239850000000001"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="10"/>
     <x v="1"/>
     <n v="172"/>
     <n v="29.441511999999999"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="10"/>
     <x v="2"/>
     <n v="92"/>
     <n v="30.696957000000001"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="10"/>
     <x v="3"/>
     <n v="238"/>
     <n v="10.186470999999999"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="10"/>
     <x v="4"/>
     <n v="271"/>
     <n v="491.75047999999998"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="10"/>
     <x v="5"/>
     <n v="115"/>
     <n v="166.35591299999999"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="11"/>
     <x v="0"/>
     <n v="122"/>
     <n v="38.908852000000003"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="11"/>
     <x v="1"/>
     <n v="122"/>
     <n v="34.416556999999997"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="11"/>
     <x v="2"/>
     <n v="58"/>
     <n v="31.831724000000001"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="11"/>
     <x v="3"/>
     <n v="168"/>
     <n v="10.040179"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="11"/>
     <x v="4"/>
     <n v="172"/>
     <n v="473.951977"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="11"/>
     <x v="5"/>
     <n v="72"/>
     <n v="158.36541700000001"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="12"/>
     <x v="0"/>
     <n v="169"/>
     <n v="32.378225"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="12"/>
     <x v="1"/>
     <n v="107"/>
     <n v="33.510561000000003"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="12"/>
     <x v="2"/>
     <n v="70"/>
     <n v="30.350428999999998"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="12"/>
     <x v="3"/>
     <n v="170"/>
     <n v="10.042"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="12"/>
     <x v="4"/>
     <n v="169"/>
     <n v="415.89313600000003"/>
   </r>
   <r>
-    <x v="3"/>
+    <n v="2025"/>
     <n v="12"/>
     <x v="5"/>
     <n v="73"/>
@@ -8047,8 +8015,172 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6B0FE92-A8F0-44F2-81AE-8F660C0D359C}" name="PivotTable7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Categories">
+  <location ref="A47:B54" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average Transactions" fld="4" subtotal="average" baseField="2" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CD5EED47-6634-433F-8246-8166C77A8301}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6" rowHeaderCaption="Territory">
+  <location ref="A7:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="% of Total_Revenue" fld="1" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4F5F414B-C686-4F7F-BA97-F099CE7B7DB1}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18" rowHeaderCaption="Store Location">
-  <location ref="A24:B36" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A25:B37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField showAll="0">
       <items count="12">
@@ -8178,180 +8310,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6B0FE92-A8F0-44F2-81AE-8F660C0D359C}" name="PivotTable7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Categories">
-  <location ref="A50:B57" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average Transactions" fld="4" subtotal="average" baseField="2" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CD5EED47-6634-433F-8246-8166C77A8301}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6" rowHeaderCaption="Territory">
-  <location ref="A7:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="% of Total_Revenue" fld="1" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="10"/>
-  </dataFields>
-  <chartFormats count="3">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6BFC6F99-E6B7-4784-8CBE-342B2F900FC9}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12" rowHeaderCaption="Year&amp;Months">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6BFC6F99-E6B7-4784-8CBE-342B2F900FC9}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
   <location ref="A1:B54" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -8995,18 +8955,18 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -9014,7 +8974,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="B3">
         <v>3417850.01</v>
@@ -9022,7 +8982,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B4">
         <v>7996850.1200000001</v>
@@ -9030,15 +8990,15 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
         <v>2</v>
@@ -9049,7 +9009,7 @@
         <v>905</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9">
         <v>637818.9</v>
@@ -9060,7 +9020,7 @@
         <v>910</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10">
         <v>351772.59</v>
@@ -9071,7 +9031,7 @@
         <v>909</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11">
         <v>330720.12</v>
@@ -9082,7 +9042,7 @@
         <v>906</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12">
         <v>312628.27</v>
@@ -9093,7 +9053,7 @@
         <v>904</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13">
         <v>298163.15999999997</v>
@@ -9104,7 +9064,7 @@
         <v>908</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14">
         <v>298111.45</v>
@@ -9115,7 +9075,7 @@
         <v>901</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15">
         <v>292987.49</v>
@@ -9126,7 +9086,7 @@
         <v>902</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16">
         <v>291145</v>
@@ -9137,7 +9097,7 @@
         <v>903</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17">
         <v>280714.34000000003</v>
@@ -9148,7 +9108,7 @@
         <v>911</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18">
         <v>269344.64000000001</v>
@@ -9159,7 +9119,7 @@
         <v>907</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19">
         <v>54444.05</v>
@@ -9167,24 +9127,24 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E23" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -9195,7 +9155,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D24">
         <v>55</v>
@@ -9212,7 +9172,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D25">
         <v>44</v>
@@ -9229,7 +9189,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D26">
         <v>28</v>
@@ -9246,7 +9206,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>69</v>
@@ -9263,7 +9223,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D28">
         <v>69</v>
@@ -9280,7 +9240,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D29">
         <v>56</v>
@@ -9297,7 +9257,7 @@
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D30">
         <v>66</v>
@@ -9314,7 +9274,7 @@
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D31">
         <v>49</v>
@@ -9331,7 +9291,7 @@
         <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D32">
         <v>23</v>
@@ -9348,7 +9308,7 @@
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D33">
         <v>50</v>
@@ -9365,7 +9325,7 @@
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D34">
         <v>80</v>
@@ -9382,7 +9342,7 @@
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D35">
         <v>56</v>
@@ -9399,7 +9359,7 @@
         <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D36">
         <v>50</v>
@@ -9416,7 +9376,7 @@
         <v>3</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D37">
         <v>42</v>
@@ -9433,7 +9393,7 @@
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D38">
         <v>29</v>
@@ -9450,7 +9410,7 @@
         <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D39">
         <v>63</v>
@@ -9467,7 +9427,7 @@
         <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D40">
         <v>63</v>
@@ -9484,7 +9444,7 @@
         <v>3</v>
       </c>
       <c r="C41" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D41">
         <v>60</v>
@@ -9501,7 +9461,7 @@
         <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D42">
         <v>35</v>
@@ -9518,7 +9478,7 @@
         <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D43">
         <v>51</v>
@@ -9535,7 +9495,7 @@
         <v>4</v>
       </c>
       <c r="C44" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D44">
         <v>31</v>
@@ -9552,7 +9512,7 @@
         <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D45">
         <v>64</v>
@@ -9569,7 +9529,7 @@
         <v>4</v>
       </c>
       <c r="C46" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D46">
         <v>82</v>
@@ -9586,7 +9546,7 @@
         <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D47">
         <v>58</v>
@@ -9603,7 +9563,7 @@
         <v>5</v>
       </c>
       <c r="C48" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D48">
         <v>55</v>
@@ -9620,7 +9580,7 @@
         <v>5</v>
       </c>
       <c r="C49" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D49">
         <v>47</v>
@@ -9637,7 +9597,7 @@
         <v>5</v>
       </c>
       <c r="C50" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D50">
         <v>26</v>
@@ -9654,7 +9614,7 @@
         <v>5</v>
       </c>
       <c r="C51" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D51">
         <v>55</v>
@@ -9671,7 +9631,7 @@
         <v>5</v>
       </c>
       <c r="C52" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D52">
         <v>79</v>
@@ -9688,7 +9648,7 @@
         <v>5</v>
       </c>
       <c r="C53" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D53">
         <v>76</v>
@@ -9705,7 +9665,7 @@
         <v>6</v>
       </c>
       <c r="C54" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D54">
         <v>62</v>
@@ -9722,7 +9682,7 @@
         <v>6</v>
       </c>
       <c r="C55" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D55">
         <v>55</v>
@@ -9739,7 +9699,7 @@
         <v>6</v>
       </c>
       <c r="C56" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D56">
         <v>26</v>
@@ -9756,7 +9716,7 @@
         <v>6</v>
       </c>
       <c r="C57" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D57">
         <v>76</v>
@@ -9773,7 +9733,7 @@
         <v>6</v>
       </c>
       <c r="C58" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -9790,7 +9750,7 @@
         <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D59">
         <v>47</v>
@@ -9807,7 +9767,7 @@
         <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D60">
         <v>48</v>
@@ -9824,7 +9784,7 @@
         <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D61">
         <v>49</v>
@@ -9841,7 +9801,7 @@
         <v>7</v>
       </c>
       <c r="C62" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D62">
         <v>26</v>
@@ -9858,7 +9818,7 @@
         <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D63">
         <v>77</v>
@@ -9875,7 +9835,7 @@
         <v>7</v>
       </c>
       <c r="C64" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D64">
         <v>66</v>
@@ -9892,7 +9852,7 @@
         <v>7</v>
       </c>
       <c r="C65" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D65">
         <v>73</v>
@@ -9909,7 +9869,7 @@
         <v>8</v>
       </c>
       <c r="C66" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D66">
         <v>57</v>
@@ -9926,7 +9886,7 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D67">
         <v>39</v>
@@ -9943,7 +9903,7 @@
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D68">
         <v>23</v>
@@ -9960,7 +9920,7 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D69">
         <v>69</v>
@@ -9977,7 +9937,7 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D70">
         <v>74</v>
@@ -9994,7 +9954,7 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D71">
         <v>60</v>
@@ -10011,7 +9971,7 @@
         <v>9</v>
       </c>
       <c r="C72" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D72">
         <v>59</v>
@@ -10028,7 +9988,7 @@
         <v>9</v>
       </c>
       <c r="C73" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D73">
         <v>52</v>
@@ -10045,7 +10005,7 @@
         <v>9</v>
       </c>
       <c r="C74" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D74">
         <v>28</v>
@@ -10062,7 +10022,7 @@
         <v>9</v>
       </c>
       <c r="C75" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D75">
         <v>70</v>
@@ -10079,7 +10039,7 @@
         <v>9</v>
       </c>
       <c r="C76" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D76">
         <v>65</v>
@@ -10096,7 +10056,7 @@
         <v>9</v>
       </c>
       <c r="C77" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D77">
         <v>60</v>
@@ -10113,7 +10073,7 @@
         <v>10</v>
       </c>
       <c r="C78" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D78">
         <v>56</v>
@@ -10130,7 +10090,7 @@
         <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D79">
         <v>56</v>
@@ -10147,7 +10107,7 @@
         <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D80">
         <v>21</v>
@@ -10164,7 +10124,7 @@
         <v>10</v>
       </c>
       <c r="C81" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D81">
         <v>75</v>
@@ -10181,7 +10141,7 @@
         <v>10</v>
       </c>
       <c r="C82" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D82">
         <v>80</v>
@@ -10198,7 +10158,7 @@
         <v>10</v>
       </c>
       <c r="C83" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D83">
         <v>69</v>
@@ -10215,7 +10175,7 @@
         <v>11</v>
       </c>
       <c r="C84" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D84">
         <v>54</v>
@@ -10232,7 +10192,7 @@
         <v>11</v>
       </c>
       <c r="C85" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D85">
         <v>41</v>
@@ -10249,7 +10209,7 @@
         <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D86">
         <v>30</v>
@@ -10266,7 +10226,7 @@
         <v>11</v>
       </c>
       <c r="C87" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D87">
         <v>71</v>
@@ -10283,7 +10243,7 @@
         <v>11</v>
       </c>
       <c r="C88" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D88">
         <v>69</v>
@@ -10300,7 +10260,7 @@
         <v>11</v>
       </c>
       <c r="C89" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D89">
         <v>57</v>
@@ -10317,7 +10277,7 @@
         <v>12</v>
       </c>
       <c r="C90" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D90">
         <v>53</v>
@@ -10334,7 +10294,7 @@
         <v>12</v>
       </c>
       <c r="C91" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D91">
         <v>50</v>
@@ -10351,7 +10311,7 @@
         <v>12</v>
       </c>
       <c r="C92" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D92">
         <v>27</v>
@@ -10368,7 +10328,7 @@
         <v>12</v>
       </c>
       <c r="C93" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D93">
         <v>61</v>
@@ -10385,7 +10345,7 @@
         <v>12</v>
       </c>
       <c r="C94" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D94">
         <v>64</v>
@@ -10402,7 +10362,7 @@
         <v>12</v>
       </c>
       <c r="C95" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D95">
         <v>60</v>
@@ -10419,7 +10379,7 @@
         <v>1</v>
       </c>
       <c r="C96" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D96">
         <v>94</v>
@@ -10436,7 +10396,7 @@
         <v>1</v>
       </c>
       <c r="C97" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D97">
         <v>74</v>
@@ -10453,7 +10413,7 @@
         <v>1</v>
       </c>
       <c r="C98" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D98">
         <v>34</v>
@@ -10470,7 +10430,7 @@
         <v>1</v>
       </c>
       <c r="C99" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D99">
         <v>87</v>
@@ -10487,7 +10447,7 @@
         <v>1</v>
       </c>
       <c r="C100" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D100">
         <v>122</v>
@@ -10504,7 +10464,7 @@
         <v>1</v>
       </c>
       <c r="C101" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D101">
         <v>51</v>
@@ -10521,7 +10481,7 @@
         <v>2</v>
       </c>
       <c r="C102" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D102">
         <v>67</v>
@@ -10538,7 +10498,7 @@
         <v>2</v>
       </c>
       <c r="C103" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D103">
         <v>78</v>
@@ -10555,7 +10515,7 @@
         <v>2</v>
       </c>
       <c r="C104" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D104">
         <v>20</v>
@@ -10572,7 +10532,7 @@
         <v>2</v>
       </c>
       <c r="C105" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D105">
         <v>89</v>
@@ -10589,7 +10549,7 @@
         <v>2</v>
       </c>
       <c r="C106" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D106">
         <v>77</v>
@@ -10606,7 +10566,7 @@
         <v>2</v>
       </c>
       <c r="C107" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D107">
         <v>57</v>
@@ -10623,7 +10583,7 @@
         <v>3</v>
       </c>
       <c r="C108" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D108">
         <v>80</v>
@@ -10640,7 +10600,7 @@
         <v>3</v>
       </c>
       <c r="C109" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D109">
         <v>52</v>
@@ -10657,7 +10617,7 @@
         <v>3</v>
       </c>
       <c r="C110" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D110">
         <v>35</v>
@@ -10674,7 +10634,7 @@
         <v>3</v>
       </c>
       <c r="C111" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D111">
         <v>90</v>
@@ -10691,7 +10651,7 @@
         <v>3</v>
       </c>
       <c r="C112" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D112">
         <v>112</v>
@@ -10708,7 +10668,7 @@
         <v>3</v>
       </c>
       <c r="C113" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D113">
         <v>60</v>
@@ -10725,7 +10685,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D114">
         <v>72</v>
@@ -10742,7 +10702,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D115">
         <v>71</v>
@@ -10759,7 +10719,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D116">
         <v>32</v>
@@ -10776,7 +10736,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D117">
         <v>127</v>
@@ -10793,7 +10753,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D118">
         <v>128</v>
@@ -10810,7 +10770,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D119">
         <v>63</v>
@@ -10827,7 +10787,7 @@
         <v>5</v>
       </c>
       <c r="C120" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D120">
         <v>72</v>
@@ -10844,7 +10804,7 @@
         <v>5</v>
       </c>
       <c r="C121" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D121">
         <v>65</v>
@@ -10861,7 +10821,7 @@
         <v>5</v>
       </c>
       <c r="C122" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D122">
         <v>36</v>
@@ -10878,7 +10838,7 @@
         <v>5</v>
       </c>
       <c r="C123" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D123">
         <v>93</v>
@@ -10895,7 +10855,7 @@
         <v>5</v>
       </c>
       <c r="C124" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D124">
         <v>107</v>
@@ -10912,7 +10872,7 @@
         <v>5</v>
       </c>
       <c r="C125" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D125">
         <v>70</v>
@@ -10929,7 +10889,7 @@
         <v>6</v>
       </c>
       <c r="C126" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D126">
         <v>56</v>
@@ -10946,7 +10906,7 @@
         <v>6</v>
       </c>
       <c r="C127" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D127">
         <v>79</v>
@@ -10963,7 +10923,7 @@
         <v>6</v>
       </c>
       <c r="C128" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D128">
         <v>38</v>
@@ -10980,7 +10940,7 @@
         <v>6</v>
       </c>
       <c r="C129" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D129">
         <v>97</v>
@@ -10997,7 +10957,7 @@
         <v>6</v>
       </c>
       <c r="C130" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D130">
         <v>107</v>
@@ -11014,7 +10974,7 @@
         <v>6</v>
       </c>
       <c r="C131" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D131">
         <v>66</v>
@@ -11031,7 +10991,7 @@
         <v>7</v>
       </c>
       <c r="C132" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D132">
         <v>88</v>
@@ -11048,7 +11008,7 @@
         <v>7</v>
       </c>
       <c r="C133" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D133">
         <v>60</v>
@@ -11065,7 +11025,7 @@
         <v>7</v>
       </c>
       <c r="C134" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -11082,7 +11042,7 @@
         <v>7</v>
       </c>
       <c r="C135" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D135">
         <v>92</v>
@@ -11099,7 +11059,7 @@
         <v>7</v>
       </c>
       <c r="C136" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D136">
         <v>98</v>
@@ -11116,7 +11076,7 @@
         <v>7</v>
       </c>
       <c r="C137" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D137">
         <v>76</v>
@@ -11133,7 +11093,7 @@
         <v>8</v>
       </c>
       <c r="C138" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D138">
         <v>70</v>
@@ -11150,7 +11110,7 @@
         <v>8</v>
       </c>
       <c r="C139" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D139">
         <v>80</v>
@@ -11167,7 +11127,7 @@
         <v>8</v>
       </c>
       <c r="C140" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D140">
         <v>35</v>
@@ -11184,7 +11144,7 @@
         <v>8</v>
       </c>
       <c r="C141" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D141">
         <v>102</v>
@@ -11201,7 +11161,7 @@
         <v>8</v>
       </c>
       <c r="C142" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D142">
         <v>91</v>
@@ -11218,7 +11178,7 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D143">
         <v>77</v>
@@ -11235,7 +11195,7 @@
         <v>9</v>
       </c>
       <c r="C144" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D144">
         <v>70</v>
@@ -11252,7 +11212,7 @@
         <v>9</v>
       </c>
       <c r="C145" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D145">
         <v>58</v>
@@ -11269,7 +11229,7 @@
         <v>9</v>
       </c>
       <c r="C146" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D146">
         <v>29</v>
@@ -11286,7 +11246,7 @@
         <v>9</v>
       </c>
       <c r="C147" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D147">
         <v>87</v>
@@ -11303,7 +11263,7 @@
         <v>9</v>
       </c>
       <c r="C148" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D148">
         <v>104</v>
@@ -11320,7 +11280,7 @@
         <v>9</v>
       </c>
       <c r="C149" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D149">
         <v>75</v>
@@ -11337,7 +11297,7 @@
         <v>10</v>
       </c>
       <c r="C150" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D150">
         <v>94</v>
@@ -11354,7 +11314,7 @@
         <v>10</v>
       </c>
       <c r="C151" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D151">
         <v>69</v>
@@ -11371,7 +11331,7 @@
         <v>10</v>
       </c>
       <c r="C152" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D152">
         <v>44</v>
@@ -11388,7 +11348,7 @@
         <v>10</v>
       </c>
       <c r="C153" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D153">
         <v>74</v>
@@ -11405,7 +11365,7 @@
         <v>10</v>
       </c>
       <c r="C154" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D154">
         <v>91</v>
@@ -11422,7 +11382,7 @@
         <v>10</v>
       </c>
       <c r="C155" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D155">
         <v>86</v>
@@ -11439,7 +11399,7 @@
         <v>11</v>
       </c>
       <c r="C156" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D156">
         <v>78</v>
@@ -11456,7 +11416,7 @@
         <v>11</v>
       </c>
       <c r="C157" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D157">
         <v>59</v>
@@ -11473,7 +11433,7 @@
         <v>11</v>
       </c>
       <c r="C158" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D158">
         <v>40</v>
@@ -11490,7 +11450,7 @@
         <v>11</v>
       </c>
       <c r="C159" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D159">
         <v>89</v>
@@ -11507,7 +11467,7 @@
         <v>11</v>
       </c>
       <c r="C160" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D160">
         <v>103</v>
@@ -11524,7 +11484,7 @@
         <v>11</v>
       </c>
       <c r="C161" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D161">
         <v>89</v>
@@ -11541,7 +11501,7 @@
         <v>12</v>
       </c>
       <c r="C162" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D162">
         <v>83</v>
@@ -11558,7 +11518,7 @@
         <v>12</v>
       </c>
       <c r="C163" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D163">
         <v>79</v>
@@ -11575,7 +11535,7 @@
         <v>12</v>
       </c>
       <c r="C164" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D164">
         <v>25</v>
@@ -11592,7 +11552,7 @@
         <v>12</v>
       </c>
       <c r="C165" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D165">
         <v>102</v>
@@ -11609,7 +11569,7 @@
         <v>12</v>
       </c>
       <c r="C166" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D166">
         <v>115</v>
@@ -11626,7 +11586,7 @@
         <v>12</v>
       </c>
       <c r="C167" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D167">
         <v>91</v>
@@ -11643,7 +11603,7 @@
         <v>1</v>
       </c>
       <c r="C168" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D168">
         <v>73</v>
@@ -11660,7 +11620,7 @@
         <v>1</v>
       </c>
       <c r="C169" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D169">
         <v>86</v>
@@ -11677,7 +11637,7 @@
         <v>1</v>
       </c>
       <c r="C170" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D170">
         <v>23</v>
@@ -11694,7 +11654,7 @@
         <v>1</v>
       </c>
       <c r="C171" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D171">
         <v>96</v>
@@ -11711,7 +11671,7 @@
         <v>1</v>
       </c>
       <c r="C172" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D172">
         <v>88</v>
@@ -11728,7 +11688,7 @@
         <v>1</v>
       </c>
       <c r="C173" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D173">
         <v>63</v>
@@ -11745,7 +11705,7 @@
         <v>2</v>
       </c>
       <c r="C174" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -11762,7 +11722,7 @@
         <v>2</v>
       </c>
       <c r="C175" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D175">
         <v>46</v>
@@ -11779,7 +11739,7 @@
         <v>2</v>
       </c>
       <c r="C176" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D176">
         <v>33</v>
@@ -11796,7 +11756,7 @@
         <v>2</v>
       </c>
       <c r="C177" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D177">
         <v>85</v>
@@ -11813,7 +11773,7 @@
         <v>2</v>
       </c>
       <c r="C178" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D178">
         <v>103</v>
@@ -11830,7 +11790,7 @@
         <v>2</v>
       </c>
       <c r="C179" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D179">
         <v>56</v>
@@ -11847,7 +11807,7 @@
         <v>3</v>
       </c>
       <c r="C180" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D180">
         <v>74</v>
@@ -11864,7 +11824,7 @@
         <v>3</v>
       </c>
       <c r="C181" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D181">
         <v>73</v>
@@ -11881,7 +11841,7 @@
         <v>3</v>
       </c>
       <c r="C182" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D182">
         <v>33</v>
@@ -11898,7 +11858,7 @@
         <v>3</v>
       </c>
       <c r="C183" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D183">
         <v>128</v>
@@ -11915,7 +11875,7 @@
         <v>3</v>
       </c>
       <c r="C184" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D184">
         <v>133</v>
@@ -11932,7 +11892,7 @@
         <v>3</v>
       </c>
       <c r="C185" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D185">
         <v>68</v>
@@ -11949,7 +11909,7 @@
         <v>4</v>
       </c>
       <c r="C186" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D186">
         <v>70</v>
@@ -11966,7 +11926,7 @@
         <v>4</v>
       </c>
       <c r="C187" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D187">
         <v>63</v>
@@ -11983,7 +11943,7 @@
         <v>4</v>
       </c>
       <c r="C188" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D188">
         <v>35</v>
@@ -12000,7 +11960,7 @@
         <v>4</v>
       </c>
       <c r="C189" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D189">
         <v>92</v>
@@ -12017,7 +11977,7 @@
         <v>4</v>
       </c>
       <c r="C190" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D190">
         <v>102</v>
@@ -12034,7 +11994,7 @@
         <v>4</v>
       </c>
       <c r="C191" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D191">
         <v>65</v>
@@ -12051,7 +12011,7 @@
         <v>5</v>
       </c>
       <c r="C192" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D192">
         <v>58</v>
@@ -12068,7 +12028,7 @@
         <v>5</v>
       </c>
       <c r="C193" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D193">
         <v>81</v>
@@ -12085,7 +12045,7 @@
         <v>5</v>
       </c>
       <c r="C194" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D194">
         <v>38</v>
@@ -12102,7 +12062,7 @@
         <v>5</v>
       </c>
       <c r="C195" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D195">
         <v>99</v>
@@ -12119,7 +12079,7 @@
         <v>5</v>
       </c>
       <c r="C196" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D196">
         <v>111</v>
@@ -12136,7 +12096,7 @@
         <v>5</v>
       </c>
       <c r="C197" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D197">
         <v>70</v>
@@ -12153,7 +12113,7 @@
         <v>6</v>
       </c>
       <c r="C198" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D198">
         <v>86</v>
@@ -12170,7 +12130,7 @@
         <v>6</v>
       </c>
       <c r="C199" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D199">
         <v>58</v>
@@ -12187,7 +12147,7 @@
         <v>6</v>
       </c>
       <c r="C200" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D200">
         <v>37</v>
@@ -12204,7 +12164,7 @@
         <v>6</v>
       </c>
       <c r="C201" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D201">
         <v>90</v>
@@ -12221,7 +12181,7 @@
         <v>6</v>
       </c>
       <c r="C202" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D202">
         <v>94</v>
@@ -12238,7 +12198,7 @@
         <v>6</v>
       </c>
       <c r="C203" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D203">
         <v>72</v>
@@ -12255,7 +12215,7 @@
         <v>7</v>
       </c>
       <c r="C204" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D204">
         <v>70</v>
@@ -12272,7 +12232,7 @@
         <v>7</v>
       </c>
       <c r="C205" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D205">
         <v>80</v>
@@ -12289,7 +12249,7 @@
         <v>7</v>
       </c>
       <c r="C206" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D206">
         <v>35</v>
@@ -12306,7 +12266,7 @@
         <v>7</v>
       </c>
       <c r="C207" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D207">
         <v>102</v>
@@ -12323,7 +12283,7 @@
         <v>7</v>
       </c>
       <c r="C208" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D208">
         <v>91</v>
@@ -12340,7 +12300,7 @@
         <v>7</v>
       </c>
       <c r="C209" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D209">
         <v>77</v>
@@ -12357,7 +12317,7 @@
         <v>8</v>
       </c>
       <c r="C210" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D210">
         <v>72</v>
@@ -12374,7 +12334,7 @@
         <v>8</v>
       </c>
       <c r="C211" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D211">
         <v>59</v>
@@ -12391,7 +12351,7 @@
         <v>8</v>
       </c>
       <c r="C212" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D212">
         <v>33</v>
@@ -12408,7 +12368,7 @@
         <v>8</v>
       </c>
       <c r="C213" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D213">
         <v>88</v>
@@ -12425,7 +12385,7 @@
         <v>8</v>
       </c>
       <c r="C214" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D214">
         <v>107</v>
@@ -12442,7 +12402,7 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D215">
         <v>79</v>
@@ -12459,7 +12419,7 @@
         <v>9</v>
       </c>
       <c r="C216" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D216">
         <v>92</v>
@@ -12476,7 +12436,7 @@
         <v>9</v>
       </c>
       <c r="C217" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D217">
         <v>68</v>
@@ -12493,7 +12453,7 @@
         <v>9</v>
       </c>
       <c r="C218" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D218">
         <v>40</v>
@@ -12510,7 +12470,7 @@
         <v>9</v>
       </c>
       <c r="C219" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D219">
         <v>73</v>
@@ -12527,7 +12487,7 @@
         <v>9</v>
       </c>
       <c r="C220" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D220">
         <v>88</v>
@@ -12544,7 +12504,7 @@
         <v>9</v>
       </c>
       <c r="C221" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D221">
         <v>82</v>
@@ -12561,7 +12521,7 @@
         <v>10</v>
       </c>
       <c r="C222" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D222">
         <v>81</v>
@@ -12578,7 +12538,7 @@
         <v>10</v>
       </c>
       <c r="C223" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D223">
         <v>60</v>
@@ -12595,7 +12555,7 @@
         <v>10</v>
       </c>
       <c r="C224" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D224">
         <v>40</v>
@@ -12612,7 +12572,7 @@
         <v>10</v>
       </c>
       <c r="C225" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D225">
         <v>97</v>
@@ -12629,7 +12589,7 @@
         <v>10</v>
       </c>
       <c r="C226" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D226">
         <v>106</v>
@@ -12646,7 +12606,7 @@
         <v>10</v>
       </c>
       <c r="C227" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D227">
         <v>93</v>
@@ -12663,7 +12623,7 @@
         <v>11</v>
       </c>
       <c r="C228" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D228">
         <v>80</v>
@@ -12680,7 +12640,7 @@
         <v>11</v>
       </c>
       <c r="C229" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D229">
         <v>78</v>
@@ -12697,7 +12657,7 @@
         <v>11</v>
       </c>
       <c r="C230" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D230">
         <v>25</v>
@@ -12714,7 +12674,7 @@
         <v>11</v>
       </c>
       <c r="C231" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D231">
         <v>94</v>
@@ -12731,7 +12691,7 @@
         <v>11</v>
       </c>
       <c r="C232" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D232">
         <v>112</v>
@@ -12748,7 +12708,7 @@
         <v>11</v>
       </c>
       <c r="C233" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D233">
         <v>87</v>
@@ -12765,7 +12725,7 @@
         <v>12</v>
       </c>
       <c r="C234" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D234">
         <v>94</v>
@@ -12782,7 +12742,7 @@
         <v>12</v>
       </c>
       <c r="C235" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D235">
         <v>74</v>
@@ -12799,7 +12759,7 @@
         <v>12</v>
       </c>
       <c r="C236" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D236">
         <v>34</v>
@@ -12816,7 +12776,7 @@
         <v>12</v>
       </c>
       <c r="C237" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D237">
         <v>87</v>
@@ -12833,7 +12793,7 @@
         <v>12</v>
       </c>
       <c r="C238" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D238">
         <v>122</v>
@@ -12850,7 +12810,7 @@
         <v>12</v>
       </c>
       <c r="C239" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D239">
         <v>51</v>
@@ -12867,7 +12827,7 @@
         <v>1</v>
       </c>
       <c r="C240" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D240">
         <v>160</v>
@@ -12884,7 +12844,7 @@
         <v>1</v>
       </c>
       <c r="C241" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D241">
         <v>127</v>
@@ -12901,7 +12861,7 @@
         <v>1</v>
       </c>
       <c r="C242" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D242">
         <v>70</v>
@@ -12918,7 +12878,7 @@
         <v>1</v>
       </c>
       <c r="C243" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D243">
         <v>197</v>
@@ -12935,7 +12895,7 @@
         <v>1</v>
       </c>
       <c r="C244" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D244">
         <v>147</v>
@@ -12952,7 +12912,7 @@
         <v>1</v>
       </c>
       <c r="C245" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D245">
         <v>50</v>
@@ -12969,7 +12929,7 @@
         <v>2</v>
       </c>
       <c r="C246" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D246">
         <v>147</v>
@@ -12986,7 +12946,7 @@
         <v>2</v>
       </c>
       <c r="C247" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D247">
         <v>100</v>
@@ -13003,7 +12963,7 @@
         <v>2</v>
       </c>
       <c r="C248" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D248">
         <v>49</v>
@@ -13020,7 +12980,7 @@
         <v>2</v>
       </c>
       <c r="C249" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D249">
         <v>183</v>
@@ -13037,7 +12997,7 @@
         <v>2</v>
       </c>
       <c r="C250" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D250">
         <v>149</v>
@@ -13054,7 +13014,7 @@
         <v>2</v>
       </c>
       <c r="C251" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D251">
         <v>44</v>
@@ -13071,7 +13031,7 @@
         <v>3</v>
       </c>
       <c r="C252" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D252">
         <v>126</v>
@@ -13088,7 +13048,7 @@
         <v>3</v>
       </c>
       <c r="C253" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D253">
         <v>121</v>
@@ -13105,7 +13065,7 @@
         <v>3</v>
       </c>
       <c r="C254" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D254">
         <v>59</v>
@@ -13122,7 +13082,7 @@
         <v>3</v>
       </c>
       <c r="C255" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D255">
         <v>166</v>
@@ -13139,7 +13099,7 @@
         <v>3</v>
       </c>
       <c r="C256" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D256">
         <v>179</v>
@@ -13156,7 +13116,7 @@
         <v>3</v>
       </c>
       <c r="C257" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D257">
         <v>65</v>
@@ -13173,7 +13133,7 @@
         <v>4</v>
       </c>
       <c r="C258" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D258">
         <v>194</v>
@@ -13190,7 +13150,7 @@
         <v>4</v>
       </c>
       <c r="C259" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D259">
         <v>169</v>
@@ -13207,7 +13167,7 @@
         <v>4</v>
       </c>
       <c r="C260" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D260">
         <v>82</v>
@@ -13224,7 +13184,7 @@
         <v>4</v>
       </c>
       <c r="C261" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D261">
         <v>226</v>
@@ -13241,7 +13201,7 @@
         <v>4</v>
       </c>
       <c r="C262" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D262">
         <v>102</v>
@@ -13258,7 +13218,7 @@
         <v>4</v>
       </c>
       <c r="C263" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D263">
         <v>98</v>
@@ -13275,7 +13235,7 @@
         <v>5</v>
       </c>
       <c r="C264" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D264">
         <v>213</v>
@@ -13292,7 +13252,7 @@
         <v>5</v>
       </c>
       <c r="C265" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D265">
         <v>175</v>
@@ -13309,7 +13269,7 @@
         <v>5</v>
       </c>
       <c r="C266" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D266">
         <v>97</v>
@@ -13326,7 +13286,7 @@
         <v>5</v>
       </c>
       <c r="C267" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D267">
         <v>267</v>
@@ -13343,7 +13303,7 @@
         <v>5</v>
       </c>
       <c r="C268" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D268">
         <v>110</v>
@@ -13360,7 +13320,7 @@
         <v>5</v>
       </c>
       <c r="C269" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D269">
         <v>103</v>
@@ -13377,7 +13337,7 @@
         <v>6</v>
       </c>
       <c r="C270" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D270">
         <v>197</v>
@@ -13394,7 +13354,7 @@
         <v>6</v>
       </c>
       <c r="C271" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D271">
         <v>140</v>
@@ -13411,7 +13371,7 @@
         <v>6</v>
       </c>
       <c r="C272" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D272">
         <v>94</v>
@@ -13428,7 +13388,7 @@
         <v>6</v>
       </c>
       <c r="C273" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D273">
         <v>256</v>
@@ -13445,7 +13405,7 @@
         <v>6</v>
       </c>
       <c r="C274" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D274">
         <v>108</v>
@@ -13462,7 +13422,7 @@
         <v>6</v>
       </c>
       <c r="C275" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D275">
         <v>119</v>
@@ -13479,7 +13439,7 @@
         <v>7</v>
       </c>
       <c r="C276" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D276">
         <v>123</v>
@@ -13496,7 +13456,7 @@
         <v>7</v>
       </c>
       <c r="C277" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D277">
         <v>113</v>
@@ -13513,7 +13473,7 @@
         <v>7</v>
       </c>
       <c r="C278" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D278">
         <v>58</v>
@@ -13530,7 +13490,7 @@
         <v>7</v>
       </c>
       <c r="C279" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D279">
         <v>141</v>
@@ -13547,7 +13507,7 @@
         <v>7</v>
       </c>
       <c r="C280" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D280">
         <v>137</v>
@@ -13564,7 +13524,7 @@
         <v>7</v>
       </c>
       <c r="C281" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D281">
         <v>76</v>
@@ -13581,7 +13541,7 @@
         <v>8</v>
       </c>
       <c r="C282" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D282">
         <v>111</v>
@@ -13598,7 +13558,7 @@
         <v>8</v>
       </c>
       <c r="C283" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D283">
         <v>95</v>
@@ -13615,7 +13575,7 @@
         <v>8</v>
       </c>
       <c r="C284" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D284">
         <v>64</v>
@@ -13632,7 +13592,7 @@
         <v>8</v>
       </c>
       <c r="C285" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D285">
         <v>167</v>
@@ -13649,7 +13609,7 @@
         <v>8</v>
       </c>
       <c r="C286" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D286">
         <v>154</v>
@@ -13666,7 +13626,7 @@
         <v>8</v>
       </c>
       <c r="C287" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D287">
         <v>78</v>
@@ -13683,7 +13643,7 @@
         <v>9</v>
       </c>
       <c r="C288" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D288">
         <v>143</v>
@@ -13700,7 +13660,7 @@
         <v>9</v>
       </c>
       <c r="C289" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D289">
         <v>121</v>
@@ -13717,7 +13677,7 @@
         <v>9</v>
       </c>
       <c r="C290" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D290">
         <v>59</v>
@@ -13734,7 +13694,7 @@
         <v>9</v>
       </c>
       <c r="C291" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D291">
         <v>157</v>
@@ -13751,7 +13711,7 @@
         <v>9</v>
       </c>
       <c r="C292" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D292">
         <v>161</v>
@@ -13768,7 +13728,7 @@
         <v>9</v>
       </c>
       <c r="C293" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D293">
         <v>74</v>
@@ -13785,7 +13745,7 @@
         <v>10</v>
       </c>
       <c r="C294" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D294">
         <v>200</v>
@@ -13802,7 +13762,7 @@
         <v>10</v>
       </c>
       <c r="C295" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D295">
         <v>172</v>
@@ -13819,7 +13779,7 @@
         <v>10</v>
       </c>
       <c r="C296" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D296">
         <v>92</v>
@@ -13836,7 +13796,7 @@
         <v>10</v>
       </c>
       <c r="C297" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D297">
         <v>238</v>
@@ -13853,7 +13813,7 @@
         <v>10</v>
       </c>
       <c r="C298" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D298">
         <v>271</v>
@@ -13870,7 +13830,7 @@
         <v>10</v>
       </c>
       <c r="C299" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D299">
         <v>115</v>
@@ -13887,7 +13847,7 @@
         <v>11</v>
       </c>
       <c r="C300" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D300">
         <v>122</v>
@@ -13904,7 +13864,7 @@
         <v>11</v>
       </c>
       <c r="C301" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D301">
         <v>122</v>
@@ -13921,7 +13881,7 @@
         <v>11</v>
       </c>
       <c r="C302" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D302">
         <v>58</v>
@@ -13938,7 +13898,7 @@
         <v>11</v>
       </c>
       <c r="C303" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D303">
         <v>168</v>
@@ -13955,7 +13915,7 @@
         <v>11</v>
       </c>
       <c r="C304" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D304">
         <v>172</v>
@@ -13972,7 +13932,7 @@
         <v>11</v>
       </c>
       <c r="C305" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D305">
         <v>72</v>
@@ -13989,7 +13949,7 @@
         <v>12</v>
       </c>
       <c r="C306" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D306">
         <v>169</v>
@@ -14006,7 +13966,7 @@
         <v>12</v>
       </c>
       <c r="C307" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D307">
         <v>107</v>
@@ -14023,7 +13983,7 @@
         <v>12</v>
       </c>
       <c r="C308" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D308">
         <v>70</v>
@@ -14040,7 +14000,7 @@
         <v>12</v>
       </c>
       <c r="C309" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D309">
         <v>170</v>
@@ -14057,7 +14017,7 @@
         <v>12</v>
       </c>
       <c r="C310" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D310">
         <v>169</v>
@@ -14074,7 +14034,7 @@
         <v>12</v>
       </c>
       <c r="C311" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D311">
         <v>73</v>
@@ -14095,25 +14055,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D34F8D5-B786-45B8-BFC3-6C1BBDFF9C48}">
-  <dimension ref="A7:B57"/>
+  <dimension ref="A7:B54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B8" s="4">
         <v>0.70057470007317668</v>
@@ -14121,7 +14081,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="B9" s="4">
         <v>0.29942529992682343</v>
@@ -14129,177 +14089,177 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="B10" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" t="s">
-        <v>19</v>
-      </c>
-    </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" s="4">
-        <v>1.5929326869437436E-2</v>
+      <c r="A25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B26" s="4">
-        <v>7.8805283793012326E-2</v>
+        <v>1.5929326869437436E-2</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B27" s="4">
-        <v>8.213184872907868E-2</v>
+        <v>7.8805283793012326E-2</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B28" s="4">
-        <v>8.5183667846208386E-2</v>
+        <v>8.213184872907868E-2</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B29" s="4">
-        <v>8.5722746505192599E-2</v>
+        <v>8.5183667846208386E-2</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B30" s="4">
-        <v>8.7221922883620059E-2</v>
+        <v>8.5722746505192599E-2</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B31" s="4">
-        <v>8.7237052277785582E-2</v>
+        <v>8.7221922883620059E-2</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B32" s="4">
-        <v>9.1469277202132118E-2</v>
+        <v>8.7237052277785582E-2</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B33" s="4">
-        <v>9.6762619492480315E-2</v>
+        <v>9.1469277202132118E-2</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B34" s="4">
-        <v>0.10292218469821034</v>
+        <v>9.6762619492480315E-2</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B35" s="4">
-        <v>0.18661406970284225</v>
+        <v>0.10292218469821034</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B36" s="4">
+        <v>0.18661406970284225</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4">
         <v>1</v>
       </c>
     </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B48">
+        <v>465.94915349999997</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B49">
+        <v>174.62502535416672</v>
+      </c>
+    </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" t="s">
-        <v>38</v>
+      <c r="A50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50">
+        <v>32.343998083333339</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B51">
-        <v>465.94915349999997</v>
+        <v>31.639881937500007</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B52">
-        <v>174.62502535416672</v>
+        <v>29.195210708333331</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B53">
-        <v>32.343998083333339</v>
+        <v>10.105105000000002</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B54">
-        <v>31.639881937500007</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B55">
-        <v>29.195210708333331</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B56">
-        <v>10.105105000000002</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B57">
         <v>123.9763957638889</v>
       </c>
     </row>
@@ -14321,10 +14281,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -14877,10 +14837,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
         <v>39</v>
-      </c>
-      <c r="B1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -15301,7 +15261,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="B54">
         <v>3417850.0100000002</v>

--- a/Chanthadara_territory_chart.xlsx
+++ b/Chanthadara_territory_chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chimm\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CADDF0E1-C1DE-49A8-9FB1-F25C5FF5DC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{68F92D3D-EA2A-45C4-A087-E766590D26D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="1" xr2:uid="{4F9622DB-3F0B-4399-96EC-3CBDB6BB25F8}"/>
   </bookViews>
@@ -8015,90 +8015,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6B0FE92-A8F0-44F2-81AE-8F660C0D359C}" name="PivotTable7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Categories">
-  <location ref="A47:B54" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="5">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average Transactions" fld="4" subtotal="average" baseField="2" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CD5EED47-6634-433F-8246-8166C77A8301}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6" rowHeaderCaption="Territory">
   <location ref="A7:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
@@ -8178,7 +8094,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4F5F414B-C686-4F7F-BA97-F099CE7B7DB1}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18" rowHeaderCaption="Store Location">
   <location ref="A25:B37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
@@ -8286,6 +8202,90 @@
   </colItems>
   <dataFields count="1">
     <dataField name="% of Revenue for Texas" fld="2" showDataAs="percentOfTotal" baseField="1" baseItem="4" numFmtId="10"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6B0FE92-A8F0-44F2-81AE-8F660C0D359C}" name="PivotTable7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Categories">
+  <location ref="A47:B54" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average Transactions" fld="4" subtotal="average" baseField="2" baseItem="0"/>
   </dataFields>
   <chartFormats count="1">
     <chartFormat chart="0" format="0" series="1">

--- a/Chanthadara_territory_chart.xlsx
+++ b/Chanthadara_territory_chart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chimm\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68F92D3D-EA2A-45C4-A087-E766590D26D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA654A1B-132C-4130-9FD3-B30698A70533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="1" xr2:uid="{4F9622DB-3F0B-4399-96EC-3CBDB6BB25F8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4F9622DB-3F0B-4399-96EC-3CBDB6BB25F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Findings" sheetId="7" r:id="rId1"/>
@@ -1068,7 +1068,6 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
-          <c:dLblPos val="inBase"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -1172,7 +1171,6 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
-          <c:dLblPos val="inBase"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -1191,7 +1189,7 @@
         <c:idx val="3"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:srgbClr val="00B0F0"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -1264,7 +1262,6 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
-          <c:dLblPos val="inBase"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -1282,10 +1279,8 @@
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -1300,19 +1295,8 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
           <c:dPt>
             <c:idx val="0"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
@@ -1331,11 +1315,10 @@
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
-            <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="00B0F0"/>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
@@ -1369,7 +1352,6 @@
                   </a:p>
                 </c:rich>
               </c:tx>
-              <c:dLblPos val="inBase"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
@@ -1406,7 +1388,6 @@
                   </a:p>
                 </c:rich>
               </c:tx>
-              <c:dLblPos val="inBase"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
@@ -1452,31 +1433,28 @@
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="inBase"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
             <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
             </c:extLst>
           </c:dLbls>
           <c:cat>
@@ -1515,194 +1493,17 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="inBase"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
+          <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
-        <c:gapWidth val="199"/>
-        <c:axId val="612561839"/>
-        <c:axId val="612552719"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="612561839"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="612552719"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="612552719"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="5000"/>
-                  <a:lumOff val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:minorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Total Revenue for Region</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="612561839"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="50"/>
+      </c:doughnutChart>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -8015,86 +7816,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CD5EED47-6634-433F-8246-8166C77A8301}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6" rowHeaderCaption="Territory">
-  <location ref="A7:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="% of Total_Revenue" fld="1" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="10"/>
-  </dataFields>
-  <chartFormats count="3">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4F5F414B-C686-4F7F-BA97-F099CE7B7DB1}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18" rowHeaderCaption="Store Location">
   <location ref="A25:B37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
@@ -8226,7 +7947,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6B0FE92-A8F0-44F2-81AE-8F660C0D359C}" name="PivotTable7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Categories">
   <location ref="A47:B54" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
@@ -8293,6 +8014,86 @@
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CD5EED47-6634-433F-8246-8166C77A8301}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7" rowHeaderCaption="Territory">
+  <location ref="A7:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="% of Total_Revenue" fld="1" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>

--- a/Chanthadara_territory_chart.xlsx
+++ b/Chanthadara_territory_chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chimm\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA654A1B-132C-4130-9FD3-B30698A70533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F16C1976-A6C4-4533-89CB-4A8BDA9C128B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4F9622DB-3F0B-4399-96EC-3CBDB6BB25F8}"/>
   </bookViews>
@@ -7816,6 +7816,86 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CD5EED47-6634-433F-8246-8166C77A8301}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7" rowHeaderCaption="Territory">
+  <location ref="A7:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="% of Total_Revenue" fld="1" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4F5F414B-C686-4F7F-BA97-F099CE7B7DB1}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18" rowHeaderCaption="Store Location">
   <location ref="A25:B37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
@@ -7947,7 +8027,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A6B0FE92-A8F0-44F2-81AE-8F660C0D359C}" name="PivotTable7" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Categories">
   <location ref="A47:B54" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
@@ -8014,86 +8094,6 @@
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CD5EED47-6634-433F-8246-8166C77A8301}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7" rowHeaderCaption="Territory">
-  <location ref="A7:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="% of Total_Revenue" fld="1" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="10"/>
-  </dataFields>
-  <chartFormats count="3">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
